--- a/data/Taller_DET_Agosto/Carga_ob/simple_time_series.xlsx
+++ b/data/Taller_DET_Agosto/Carga_ob/simple_time_series.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MarginalCost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Shifts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NodeAssignment" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="StationAssignment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ExtractionGoal" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30091,7 +30091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33266,11 +33266,6 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr"/>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Taller_DET_Agosto/Carga_ob/simple_time_series.xlsx
+++ b/data/Taller_DET_Agosto/Carga_ob/simple_time_series.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1096"/>
+  <dimension ref="A1:G1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,6 +562,11 @@
           <t>duration</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>base_hour</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -584,6 +589,9 @@
       <c r="F2" t="n">
         <v>8</v>
       </c>
+      <c r="G2" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -606,6 +614,7 @@
       <c r="F3" t="n">
         <v>8</v>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -628,6 +637,7 @@
       <c r="F4" t="n">
         <v>8</v>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -650,6 +660,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -672,6 +683,7 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -694,6 +706,7 @@
       <c r="F7" t="n">
         <v>8</v>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -716,6 +729,7 @@
       <c r="F8" t="n">
         <v>8</v>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -738,6 +752,7 @@
       <c r="F9" t="n">
         <v>8</v>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -760,6 +775,7 @@
       <c r="F10" t="n">
         <v>8</v>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -782,6 +798,7 @@
       <c r="F11" t="n">
         <v>8</v>
       </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -804,6 +821,7 @@
       <c r="F12" t="n">
         <v>8</v>
       </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -826,6 +844,7 @@
       <c r="F13" t="n">
         <v>8</v>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -848,6 +867,7 @@
       <c r="F14" t="n">
         <v>8</v>
       </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -870,6 +890,7 @@
       <c r="F15" t="n">
         <v>8</v>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -892,6 +913,7 @@
       <c r="F16" t="n">
         <v>8</v>
       </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -914,6 +936,7 @@
       <c r="F17" t="n">
         <v>8</v>
       </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -936,6 +959,7 @@
       <c r="F18" t="n">
         <v>8</v>
       </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -958,6 +982,7 @@
       <c r="F19" t="n">
         <v>8</v>
       </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -980,6 +1005,7 @@
       <c r="F20" t="n">
         <v>8</v>
       </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1002,6 +1028,7 @@
       <c r="F21" t="n">
         <v>8</v>
       </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1024,6 +1051,7 @@
       <c r="F22" t="n">
         <v>8</v>
       </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1046,6 +1074,7 @@
       <c r="F23" t="n">
         <v>8</v>
       </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1068,6 +1097,7 @@
       <c r="F24" t="n">
         <v>8</v>
       </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1090,6 +1120,7 @@
       <c r="F25" t="n">
         <v>8</v>
       </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1112,6 +1143,7 @@
       <c r="F26" t="n">
         <v>8</v>
       </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1134,6 +1166,7 @@
       <c r="F27" t="n">
         <v>8</v>
       </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1156,6 +1189,7 @@
       <c r="F28" t="n">
         <v>8</v>
       </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1178,6 +1212,7 @@
       <c r="F29" t="n">
         <v>8</v>
       </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1200,6 +1235,7 @@
       <c r="F30" t="n">
         <v>8</v>
       </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1222,6 +1258,7 @@
       <c r="F31" t="n">
         <v>8</v>
       </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1244,6 +1281,7 @@
       <c r="F32" t="n">
         <v>8</v>
       </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1266,6 +1304,7 @@
       <c r="F33" t="n">
         <v>8</v>
       </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1288,6 +1327,7 @@
       <c r="F34" t="n">
         <v>8</v>
       </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1310,6 +1350,7 @@
       <c r="F35" t="n">
         <v>8</v>
       </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1332,6 +1373,7 @@
       <c r="F36" t="n">
         <v>8</v>
       </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1354,6 +1396,7 @@
       <c r="F37" t="n">
         <v>8</v>
       </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1376,6 +1419,7 @@
       <c r="F38" t="n">
         <v>8</v>
       </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1398,6 +1442,7 @@
       <c r="F39" t="n">
         <v>8</v>
       </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1420,6 +1465,7 @@
       <c r="F40" t="n">
         <v>8</v>
       </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1442,6 +1488,7 @@
       <c r="F41" t="n">
         <v>8</v>
       </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1464,6 +1511,7 @@
       <c r="F42" t="n">
         <v>8</v>
       </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1486,6 +1534,7 @@
       <c r="F43" t="n">
         <v>8</v>
       </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1508,6 +1557,7 @@
       <c r="F44" t="n">
         <v>8</v>
       </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1530,6 +1580,7 @@
       <c r="F45" t="n">
         <v>8</v>
       </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1552,6 +1603,7 @@
       <c r="F46" t="n">
         <v>8</v>
       </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1574,6 +1626,7 @@
       <c r="F47" t="n">
         <v>8</v>
       </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1596,6 +1649,7 @@
       <c r="F48" t="n">
         <v>8</v>
       </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1618,6 +1672,7 @@
       <c r="F49" t="n">
         <v>8</v>
       </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1640,6 +1695,7 @@
       <c r="F50" t="n">
         <v>8</v>
       </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1662,6 +1718,7 @@
       <c r="F51" t="n">
         <v>8</v>
       </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1684,6 +1741,7 @@
       <c r="F52" t="n">
         <v>8</v>
       </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1706,6 +1764,7 @@
       <c r="F53" t="n">
         <v>8</v>
       </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1728,6 +1787,7 @@
       <c r="F54" t="n">
         <v>8</v>
       </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1750,6 +1810,7 @@
       <c r="F55" t="n">
         <v>8</v>
       </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1772,6 +1833,7 @@
       <c r="F56" t="n">
         <v>8</v>
       </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1794,6 +1856,7 @@
       <c r="F57" t="n">
         <v>8</v>
       </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1816,6 +1879,7 @@
       <c r="F58" t="n">
         <v>8</v>
       </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1838,6 +1902,7 @@
       <c r="F59" t="n">
         <v>8</v>
       </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1860,6 +1925,7 @@
       <c r="F60" t="n">
         <v>8</v>
       </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1882,6 +1948,7 @@
       <c r="F61" t="n">
         <v>8</v>
       </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1904,6 +1971,7 @@
       <c r="F62" t="n">
         <v>8</v>
       </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1926,6 +1994,7 @@
       <c r="F63" t="n">
         <v>8</v>
       </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1948,6 +2017,7 @@
       <c r="F64" t="n">
         <v>8</v>
       </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1970,6 +2040,7 @@
       <c r="F65" t="n">
         <v>8</v>
       </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1992,6 +2063,7 @@
       <c r="F66" t="n">
         <v>8</v>
       </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2014,6 +2086,7 @@
       <c r="F67" t="n">
         <v>8</v>
       </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2036,6 +2109,7 @@
       <c r="F68" t="n">
         <v>8</v>
       </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2058,6 +2132,7 @@
       <c r="F69" t="n">
         <v>8</v>
       </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2080,6 +2155,7 @@
       <c r="F70" t="n">
         <v>8</v>
       </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2102,6 +2178,7 @@
       <c r="F71" t="n">
         <v>8</v>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2124,6 +2201,7 @@
       <c r="F72" t="n">
         <v>8</v>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2146,6 +2224,7 @@
       <c r="F73" t="n">
         <v>8</v>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2168,6 +2247,7 @@
       <c r="F74" t="n">
         <v>8</v>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2190,6 +2270,7 @@
       <c r="F75" t="n">
         <v>8</v>
       </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2212,6 +2293,7 @@
       <c r="F76" t="n">
         <v>8</v>
       </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2234,6 +2316,7 @@
       <c r="F77" t="n">
         <v>8</v>
       </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2256,6 +2339,7 @@
       <c r="F78" t="n">
         <v>8</v>
       </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2278,6 +2362,7 @@
       <c r="F79" t="n">
         <v>8</v>
       </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2300,6 +2385,7 @@
       <c r="F80" t="n">
         <v>8</v>
       </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2322,6 +2408,7 @@
       <c r="F81" t="n">
         <v>8</v>
       </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2344,6 +2431,7 @@
       <c r="F82" t="n">
         <v>8</v>
       </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2366,6 +2454,7 @@
       <c r="F83" t="n">
         <v>8</v>
       </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2388,6 +2477,7 @@
       <c r="F84" t="n">
         <v>8</v>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2410,6 +2500,7 @@
       <c r="F85" t="n">
         <v>8</v>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2432,6 +2523,7 @@
       <c r="F86" t="n">
         <v>8</v>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2454,6 +2546,7 @@
       <c r="F87" t="n">
         <v>8</v>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2476,6 +2569,7 @@
       <c r="F88" t="n">
         <v>8</v>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2498,6 +2592,7 @@
       <c r="F89" t="n">
         <v>8</v>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2520,6 +2615,7 @@
       <c r="F90" t="n">
         <v>8</v>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2542,6 +2638,7 @@
       <c r="F91" t="n">
         <v>8</v>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2564,6 +2661,7 @@
       <c r="F92" t="n">
         <v>8</v>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2586,6 +2684,7 @@
       <c r="F93" t="n">
         <v>8</v>
       </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2608,6 +2707,7 @@
       <c r="F94" t="n">
         <v>8</v>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2630,6 +2730,7 @@
       <c r="F95" t="n">
         <v>8</v>
       </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2652,6 +2753,7 @@
       <c r="F96" t="n">
         <v>8</v>
       </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2674,6 +2776,7 @@
       <c r="F97" t="n">
         <v>8</v>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2696,6 +2799,7 @@
       <c r="F98" t="n">
         <v>8</v>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2718,6 +2822,7 @@
       <c r="F99" t="n">
         <v>8</v>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2740,6 +2845,7 @@
       <c r="F100" t="n">
         <v>8</v>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2762,6 +2868,7 @@
       <c r="F101" t="n">
         <v>8</v>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2784,6 +2891,7 @@
       <c r="F102" t="n">
         <v>8</v>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2806,6 +2914,7 @@
       <c r="F103" t="n">
         <v>8</v>
       </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2828,6 +2937,7 @@
       <c r="F104" t="n">
         <v>8</v>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2850,6 +2960,7 @@
       <c r="F105" t="n">
         <v>8</v>
       </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2872,6 +2983,7 @@
       <c r="F106" t="n">
         <v>8</v>
       </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2894,6 +3006,7 @@
       <c r="F107" t="n">
         <v>8</v>
       </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2916,6 +3029,7 @@
       <c r="F108" t="n">
         <v>8</v>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2938,6 +3052,7 @@
       <c r="F109" t="n">
         <v>8</v>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2960,6 +3075,7 @@
       <c r="F110" t="n">
         <v>8</v>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2982,6 +3098,7 @@
       <c r="F111" t="n">
         <v>8</v>
       </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3004,6 +3121,7 @@
       <c r="F112" t="n">
         <v>8</v>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3026,6 +3144,7 @@
       <c r="F113" t="n">
         <v>8</v>
       </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3048,6 +3167,7 @@
       <c r="F114" t="n">
         <v>8</v>
       </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3070,6 +3190,7 @@
       <c r="F115" t="n">
         <v>8</v>
       </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3092,6 +3213,7 @@
       <c r="F116" t="n">
         <v>8</v>
       </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3114,6 +3236,7 @@
       <c r="F117" t="n">
         <v>8</v>
       </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3136,6 +3259,7 @@
       <c r="F118" t="n">
         <v>8</v>
       </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3158,6 +3282,7 @@
       <c r="F119" t="n">
         <v>8</v>
       </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3180,6 +3305,7 @@
       <c r="F120" t="n">
         <v>8</v>
       </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3202,6 +3328,7 @@
       <c r="F121" t="n">
         <v>8</v>
       </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3224,6 +3351,7 @@
       <c r="F122" t="n">
         <v>8</v>
       </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3246,6 +3374,7 @@
       <c r="F123" t="n">
         <v>8</v>
       </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3268,6 +3397,7 @@
       <c r="F124" t="n">
         <v>8</v>
       </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3290,6 +3420,7 @@
       <c r="F125" t="n">
         <v>8</v>
       </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3312,6 +3443,7 @@
       <c r="F126" t="n">
         <v>8</v>
       </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3334,6 +3466,7 @@
       <c r="F127" t="n">
         <v>8</v>
       </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3356,6 +3489,7 @@
       <c r="F128" t="n">
         <v>8</v>
       </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3378,6 +3512,7 @@
       <c r="F129" t="n">
         <v>8</v>
       </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3400,6 +3535,7 @@
       <c r="F130" t="n">
         <v>8</v>
       </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3422,6 +3558,7 @@
       <c r="F131" t="n">
         <v>8</v>
       </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3444,6 +3581,7 @@
       <c r="F132" t="n">
         <v>8</v>
       </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3466,6 +3604,7 @@
       <c r="F133" t="n">
         <v>8</v>
       </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3488,6 +3627,7 @@
       <c r="F134" t="n">
         <v>8</v>
       </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3510,6 +3650,7 @@
       <c r="F135" t="n">
         <v>8</v>
       </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3532,6 +3673,7 @@
       <c r="F136" t="n">
         <v>8</v>
       </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3554,6 +3696,7 @@
       <c r="F137" t="n">
         <v>8</v>
       </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3576,6 +3719,7 @@
       <c r="F138" t="n">
         <v>8</v>
       </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3598,6 +3742,7 @@
       <c r="F139" t="n">
         <v>8</v>
       </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3620,6 +3765,7 @@
       <c r="F140" t="n">
         <v>8</v>
       </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3642,6 +3788,7 @@
       <c r="F141" t="n">
         <v>8</v>
       </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3664,6 +3811,7 @@
       <c r="F142" t="n">
         <v>8</v>
       </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3686,6 +3834,7 @@
       <c r="F143" t="n">
         <v>8</v>
       </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3708,6 +3857,7 @@
       <c r="F144" t="n">
         <v>8</v>
       </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3730,6 +3880,7 @@
       <c r="F145" t="n">
         <v>8</v>
       </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3752,6 +3903,7 @@
       <c r="F146" t="n">
         <v>8</v>
       </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3774,6 +3926,7 @@
       <c r="F147" t="n">
         <v>8</v>
       </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3796,6 +3949,7 @@
       <c r="F148" t="n">
         <v>8</v>
       </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3818,6 +3972,7 @@
       <c r="F149" t="n">
         <v>8</v>
       </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3840,6 +3995,7 @@
       <c r="F150" t="n">
         <v>8</v>
       </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3862,6 +4018,7 @@
       <c r="F151" t="n">
         <v>8</v>
       </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3884,6 +4041,7 @@
       <c r="F152" t="n">
         <v>8</v>
       </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3906,6 +4064,7 @@
       <c r="F153" t="n">
         <v>8</v>
       </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3928,6 +4087,7 @@
       <c r="F154" t="n">
         <v>8</v>
       </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3950,6 +4110,7 @@
       <c r="F155" t="n">
         <v>8</v>
       </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3972,6 +4133,7 @@
       <c r="F156" t="n">
         <v>8</v>
       </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3994,6 +4156,7 @@
       <c r="F157" t="n">
         <v>8</v>
       </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4016,6 +4179,7 @@
       <c r="F158" t="n">
         <v>8</v>
       </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4038,6 +4202,7 @@
       <c r="F159" t="n">
         <v>8</v>
       </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4060,6 +4225,7 @@
       <c r="F160" t="n">
         <v>8</v>
       </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4082,6 +4248,7 @@
       <c r="F161" t="n">
         <v>8</v>
       </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4104,6 +4271,7 @@
       <c r="F162" t="n">
         <v>8</v>
       </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4126,6 +4294,7 @@
       <c r="F163" t="n">
         <v>8</v>
       </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4148,6 +4317,7 @@
       <c r="F164" t="n">
         <v>8</v>
       </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4170,6 +4340,7 @@
       <c r="F165" t="n">
         <v>8</v>
       </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4192,6 +4363,7 @@
       <c r="F166" t="n">
         <v>8</v>
       </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4214,6 +4386,7 @@
       <c r="F167" t="n">
         <v>8</v>
       </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4236,6 +4409,7 @@
       <c r="F168" t="n">
         <v>8</v>
       </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4258,6 +4432,7 @@
       <c r="F169" t="n">
         <v>8</v>
       </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4280,6 +4455,7 @@
       <c r="F170" t="n">
         <v>8</v>
       </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4302,6 +4478,7 @@
       <c r="F171" t="n">
         <v>8</v>
       </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4324,6 +4501,7 @@
       <c r="F172" t="n">
         <v>8</v>
       </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4346,6 +4524,7 @@
       <c r="F173" t="n">
         <v>8</v>
       </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4368,6 +4547,7 @@
       <c r="F174" t="n">
         <v>8</v>
       </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4390,6 +4570,7 @@
       <c r="F175" t="n">
         <v>8</v>
       </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4412,6 +4593,7 @@
       <c r="F176" t="n">
         <v>8</v>
       </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4434,6 +4616,7 @@
       <c r="F177" t="n">
         <v>8</v>
       </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4456,6 +4639,7 @@
       <c r="F178" t="n">
         <v>8</v>
       </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4478,6 +4662,7 @@
       <c r="F179" t="n">
         <v>8</v>
       </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4500,6 +4685,7 @@
       <c r="F180" t="n">
         <v>8</v>
       </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4522,6 +4708,7 @@
       <c r="F181" t="n">
         <v>8</v>
       </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4544,6 +4731,7 @@
       <c r="F182" t="n">
         <v>8</v>
       </c>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4566,6 +4754,7 @@
       <c r="F183" t="n">
         <v>8</v>
       </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4588,6 +4777,7 @@
       <c r="F184" t="n">
         <v>8</v>
       </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4610,6 +4800,7 @@
       <c r="F185" t="n">
         <v>8</v>
       </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4632,6 +4823,7 @@
       <c r="F186" t="n">
         <v>8</v>
       </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4654,6 +4846,7 @@
       <c r="F187" t="n">
         <v>8</v>
       </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4676,6 +4869,7 @@
       <c r="F188" t="n">
         <v>8</v>
       </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4698,6 +4892,7 @@
       <c r="F189" t="n">
         <v>8</v>
       </c>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4720,6 +4915,7 @@
       <c r="F190" t="n">
         <v>8</v>
       </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4742,6 +4938,7 @@
       <c r="F191" t="n">
         <v>8</v>
       </c>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4764,6 +4961,7 @@
       <c r="F192" t="n">
         <v>8</v>
       </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4786,6 +4984,7 @@
       <c r="F193" t="n">
         <v>8</v>
       </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4808,6 +5007,7 @@
       <c r="F194" t="n">
         <v>8</v>
       </c>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4830,6 +5030,7 @@
       <c r="F195" t="n">
         <v>8</v>
       </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4852,6 +5053,7 @@
       <c r="F196" t="n">
         <v>8</v>
       </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4874,6 +5076,7 @@
       <c r="F197" t="n">
         <v>8</v>
       </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4896,6 +5099,7 @@
       <c r="F198" t="n">
         <v>8</v>
       </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4918,6 +5122,7 @@
       <c r="F199" t="n">
         <v>8</v>
       </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4940,6 +5145,7 @@
       <c r="F200" t="n">
         <v>8</v>
       </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4962,6 +5168,7 @@
       <c r="F201" t="n">
         <v>8</v>
       </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4984,6 +5191,7 @@
       <c r="F202" t="n">
         <v>8</v>
       </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5006,6 +5214,7 @@
       <c r="F203" t="n">
         <v>8</v>
       </c>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5028,6 +5237,7 @@
       <c r="F204" t="n">
         <v>8</v>
       </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -5050,6 +5260,7 @@
       <c r="F205" t="n">
         <v>8</v>
       </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5072,6 +5283,7 @@
       <c r="F206" t="n">
         <v>8</v>
       </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5094,6 +5306,7 @@
       <c r="F207" t="n">
         <v>8</v>
       </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5116,6 +5329,7 @@
       <c r="F208" t="n">
         <v>8</v>
       </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5138,6 +5352,7 @@
       <c r="F209" t="n">
         <v>8</v>
       </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5160,6 +5375,7 @@
       <c r="F210" t="n">
         <v>8</v>
       </c>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5182,6 +5398,7 @@
       <c r="F211" t="n">
         <v>8</v>
       </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5204,6 +5421,7 @@
       <c r="F212" t="n">
         <v>8</v>
       </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5226,6 +5444,7 @@
       <c r="F213" t="n">
         <v>8</v>
       </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -5248,6 +5467,7 @@
       <c r="F214" t="n">
         <v>8</v>
       </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -5270,6 +5490,7 @@
       <c r="F215" t="n">
         <v>8</v>
       </c>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -5292,6 +5513,7 @@
       <c r="F216" t="n">
         <v>8</v>
       </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5314,6 +5536,7 @@
       <c r="F217" t="n">
         <v>8</v>
       </c>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -5336,6 +5559,7 @@
       <c r="F218" t="n">
         <v>8</v>
       </c>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5358,6 +5582,7 @@
       <c r="F219" t="n">
         <v>8</v>
       </c>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5380,6 +5605,7 @@
       <c r="F220" t="n">
         <v>8</v>
       </c>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5402,6 +5628,7 @@
       <c r="F221" t="n">
         <v>8</v>
       </c>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5424,6 +5651,7 @@
       <c r="F222" t="n">
         <v>8</v>
       </c>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5446,6 +5674,7 @@
       <c r="F223" t="n">
         <v>8</v>
       </c>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5468,6 +5697,7 @@
       <c r="F224" t="n">
         <v>8</v>
       </c>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -5490,6 +5720,7 @@
       <c r="F225" t="n">
         <v>8</v>
       </c>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -5512,6 +5743,7 @@
       <c r="F226" t="n">
         <v>8</v>
       </c>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -5534,6 +5766,7 @@
       <c r="F227" t="n">
         <v>8</v>
       </c>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -5556,6 +5789,7 @@
       <c r="F228" t="n">
         <v>8</v>
       </c>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5578,6 +5812,7 @@
       <c r="F229" t="n">
         <v>8</v>
       </c>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5600,6 +5835,7 @@
       <c r="F230" t="n">
         <v>8</v>
       </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5622,6 +5858,7 @@
       <c r="F231" t="n">
         <v>8</v>
       </c>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5644,6 +5881,7 @@
       <c r="F232" t="n">
         <v>8</v>
       </c>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5666,6 +5904,7 @@
       <c r="F233" t="n">
         <v>8</v>
       </c>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5688,6 +5927,7 @@
       <c r="F234" t="n">
         <v>8</v>
       </c>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5710,6 +5950,7 @@
       <c r="F235" t="n">
         <v>8</v>
       </c>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5732,6 +5973,7 @@
       <c r="F236" t="n">
         <v>8</v>
       </c>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5754,6 +5996,7 @@
       <c r="F237" t="n">
         <v>8</v>
       </c>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5776,6 +6019,7 @@
       <c r="F238" t="n">
         <v>8</v>
       </c>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5798,6 +6042,7 @@
       <c r="F239" t="n">
         <v>8</v>
       </c>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5820,6 +6065,7 @@
       <c r="F240" t="n">
         <v>8</v>
       </c>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5842,6 +6088,7 @@
       <c r="F241" t="n">
         <v>8</v>
       </c>
+      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -5864,6 +6111,7 @@
       <c r="F242" t="n">
         <v>8</v>
       </c>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -5886,6 +6134,7 @@
       <c r="F243" t="n">
         <v>8</v>
       </c>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -5908,6 +6157,7 @@
       <c r="F244" t="n">
         <v>8</v>
       </c>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -5930,6 +6180,7 @@
       <c r="F245" t="n">
         <v>8</v>
       </c>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -5952,6 +6203,7 @@
       <c r="F246" t="n">
         <v>8</v>
       </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -5974,6 +6226,7 @@
       <c r="F247" t="n">
         <v>8</v>
       </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -5996,6 +6249,7 @@
       <c r="F248" t="n">
         <v>8</v>
       </c>
+      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -6018,6 +6272,7 @@
       <c r="F249" t="n">
         <v>8</v>
       </c>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -6040,6 +6295,7 @@
       <c r="F250" t="n">
         <v>8</v>
       </c>
+      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -6062,6 +6318,7 @@
       <c r="F251" t="n">
         <v>8</v>
       </c>
+      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -6084,6 +6341,7 @@
       <c r="F252" t="n">
         <v>8</v>
       </c>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -6106,6 +6364,7 @@
       <c r="F253" t="n">
         <v>8</v>
       </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -6128,6 +6387,7 @@
       <c r="F254" t="n">
         <v>8</v>
       </c>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -6150,6 +6410,7 @@
       <c r="F255" t="n">
         <v>8</v>
       </c>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -6172,6 +6433,7 @@
       <c r="F256" t="n">
         <v>8</v>
       </c>
+      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -6194,6 +6456,7 @@
       <c r="F257" t="n">
         <v>8</v>
       </c>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -6216,6 +6479,7 @@
       <c r="F258" t="n">
         <v>8</v>
       </c>
+      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -6238,6 +6502,7 @@
       <c r="F259" t="n">
         <v>8</v>
       </c>
+      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -6260,6 +6525,7 @@
       <c r="F260" t="n">
         <v>8</v>
       </c>
+      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -6282,6 +6548,7 @@
       <c r="F261" t="n">
         <v>8</v>
       </c>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -6304,6 +6571,7 @@
       <c r="F262" t="n">
         <v>8</v>
       </c>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -6326,6 +6594,7 @@
       <c r="F263" t="n">
         <v>8</v>
       </c>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -6348,6 +6617,7 @@
       <c r="F264" t="n">
         <v>8</v>
       </c>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -6370,6 +6640,7 @@
       <c r="F265" t="n">
         <v>8</v>
       </c>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -6392,6 +6663,7 @@
       <c r="F266" t="n">
         <v>8</v>
       </c>
+      <c r="G266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -6414,6 +6686,7 @@
       <c r="F267" t="n">
         <v>8</v>
       </c>
+      <c r="G267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -6436,6 +6709,7 @@
       <c r="F268" t="n">
         <v>8</v>
       </c>
+      <c r="G268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -6458,6 +6732,7 @@
       <c r="F269" t="n">
         <v>8</v>
       </c>
+      <c r="G269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -6480,6 +6755,7 @@
       <c r="F270" t="n">
         <v>8</v>
       </c>
+      <c r="G270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -6502,6 +6778,7 @@
       <c r="F271" t="n">
         <v>8</v>
       </c>
+      <c r="G271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -6524,6 +6801,7 @@
       <c r="F272" t="n">
         <v>8</v>
       </c>
+      <c r="G272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -6546,6 +6824,7 @@
       <c r="F273" t="n">
         <v>8</v>
       </c>
+      <c r="G273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -6568,6 +6847,7 @@
       <c r="F274" t="n">
         <v>8</v>
       </c>
+      <c r="G274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -6590,6 +6870,7 @@
       <c r="F275" t="n">
         <v>8</v>
       </c>
+      <c r="G275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -6612,6 +6893,7 @@
       <c r="F276" t="n">
         <v>8</v>
       </c>
+      <c r="G276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -6634,6 +6916,7 @@
       <c r="F277" t="n">
         <v>8</v>
       </c>
+      <c r="G277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -6656,6 +6939,7 @@
       <c r="F278" t="n">
         <v>8</v>
       </c>
+      <c r="G278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -6678,6 +6962,7 @@
       <c r="F279" t="n">
         <v>8</v>
       </c>
+      <c r="G279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -6700,6 +6985,7 @@
       <c r="F280" t="n">
         <v>8</v>
       </c>
+      <c r="G280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -6722,6 +7008,7 @@
       <c r="F281" t="n">
         <v>8</v>
       </c>
+      <c r="G281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -6744,6 +7031,7 @@
       <c r="F282" t="n">
         <v>8</v>
       </c>
+      <c r="G282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -6766,6 +7054,7 @@
       <c r="F283" t="n">
         <v>8</v>
       </c>
+      <c r="G283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -6788,6 +7077,7 @@
       <c r="F284" t="n">
         <v>8</v>
       </c>
+      <c r="G284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -6810,6 +7100,7 @@
       <c r="F285" t="n">
         <v>8</v>
       </c>
+      <c r="G285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -6832,6 +7123,7 @@
       <c r="F286" t="n">
         <v>8</v>
       </c>
+      <c r="G286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -6854,6 +7146,7 @@
       <c r="F287" t="n">
         <v>8</v>
       </c>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -6876,6 +7169,7 @@
       <c r="F288" t="n">
         <v>8</v>
       </c>
+      <c r="G288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -6898,6 +7192,7 @@
       <c r="F289" t="n">
         <v>8</v>
       </c>
+      <c r="G289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -6920,6 +7215,7 @@
       <c r="F290" t="n">
         <v>8</v>
       </c>
+      <c r="G290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -6942,6 +7238,7 @@
       <c r="F291" t="n">
         <v>8</v>
       </c>
+      <c r="G291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -6964,6 +7261,7 @@
       <c r="F292" t="n">
         <v>8</v>
       </c>
+      <c r="G292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -6986,6 +7284,7 @@
       <c r="F293" t="n">
         <v>8</v>
       </c>
+      <c r="G293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -7008,6 +7307,7 @@
       <c r="F294" t="n">
         <v>8</v>
       </c>
+      <c r="G294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -7030,6 +7330,7 @@
       <c r="F295" t="n">
         <v>8</v>
       </c>
+      <c r="G295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -7052,6 +7353,7 @@
       <c r="F296" t="n">
         <v>8</v>
       </c>
+      <c r="G296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -7074,6 +7376,7 @@
       <c r="F297" t="n">
         <v>8</v>
       </c>
+      <c r="G297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -7096,6 +7399,7 @@
       <c r="F298" t="n">
         <v>8</v>
       </c>
+      <c r="G298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -7118,6 +7422,7 @@
       <c r="F299" t="n">
         <v>8</v>
       </c>
+      <c r="G299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -7140,6 +7445,7 @@
       <c r="F300" t="n">
         <v>8</v>
       </c>
+      <c r="G300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -7162,6 +7468,7 @@
       <c r="F301" t="n">
         <v>8</v>
       </c>
+      <c r="G301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -7184,6 +7491,7 @@
       <c r="F302" t="n">
         <v>8</v>
       </c>
+      <c r="G302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -7206,6 +7514,7 @@
       <c r="F303" t="n">
         <v>8</v>
       </c>
+      <c r="G303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -7228,6 +7537,7 @@
       <c r="F304" t="n">
         <v>8</v>
       </c>
+      <c r="G304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -7250,6 +7560,7 @@
       <c r="F305" t="n">
         <v>8</v>
       </c>
+      <c r="G305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -7272,6 +7583,7 @@
       <c r="F306" t="n">
         <v>8</v>
       </c>
+      <c r="G306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -7294,6 +7606,7 @@
       <c r="F307" t="n">
         <v>8</v>
       </c>
+      <c r="G307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -7316,6 +7629,7 @@
       <c r="F308" t="n">
         <v>8</v>
       </c>
+      <c r="G308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -7338,6 +7652,7 @@
       <c r="F309" t="n">
         <v>8</v>
       </c>
+      <c r="G309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -7360,6 +7675,7 @@
       <c r="F310" t="n">
         <v>8</v>
       </c>
+      <c r="G310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -7382,6 +7698,7 @@
       <c r="F311" t="n">
         <v>8</v>
       </c>
+      <c r="G311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -7404,6 +7721,7 @@
       <c r="F312" t="n">
         <v>8</v>
       </c>
+      <c r="G312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7426,6 +7744,7 @@
       <c r="F313" t="n">
         <v>8</v>
       </c>
+      <c r="G313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7448,6 +7767,7 @@
       <c r="F314" t="n">
         <v>8</v>
       </c>
+      <c r="G314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7470,6 +7790,7 @@
       <c r="F315" t="n">
         <v>8</v>
       </c>
+      <c r="G315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -7492,6 +7813,7 @@
       <c r="F316" t="n">
         <v>8</v>
       </c>
+      <c r="G316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -7514,6 +7836,7 @@
       <c r="F317" t="n">
         <v>8</v>
       </c>
+      <c r="G317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -7536,6 +7859,7 @@
       <c r="F318" t="n">
         <v>8</v>
       </c>
+      <c r="G318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -7558,6 +7882,7 @@
       <c r="F319" t="n">
         <v>8</v>
       </c>
+      <c r="G319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -7580,6 +7905,7 @@
       <c r="F320" t="n">
         <v>8</v>
       </c>
+      <c r="G320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -7602,6 +7928,7 @@
       <c r="F321" t="n">
         <v>8</v>
       </c>
+      <c r="G321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -7624,6 +7951,7 @@
       <c r="F322" t="n">
         <v>8</v>
       </c>
+      <c r="G322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -7646,6 +7974,7 @@
       <c r="F323" t="n">
         <v>8</v>
       </c>
+      <c r="G323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -7668,6 +7997,7 @@
       <c r="F324" t="n">
         <v>8</v>
       </c>
+      <c r="G324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -7690,6 +8020,7 @@
       <c r="F325" t="n">
         <v>8</v>
       </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -7712,6 +8043,7 @@
       <c r="F326" t="n">
         <v>8</v>
       </c>
+      <c r="G326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -7734,6 +8066,7 @@
       <c r="F327" t="n">
         <v>8</v>
       </c>
+      <c r="G327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -7756,6 +8089,7 @@
       <c r="F328" t="n">
         <v>8</v>
       </c>
+      <c r="G328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -7778,6 +8112,7 @@
       <c r="F329" t="n">
         <v>8</v>
       </c>
+      <c r="G329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -7800,6 +8135,7 @@
       <c r="F330" t="n">
         <v>8</v>
       </c>
+      <c r="G330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7822,6 +8158,7 @@
       <c r="F331" t="n">
         <v>8</v>
       </c>
+      <c r="G331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -7844,6 +8181,7 @@
       <c r="F332" t="n">
         <v>8</v>
       </c>
+      <c r="G332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -7866,6 +8204,7 @@
       <c r="F333" t="n">
         <v>8</v>
       </c>
+      <c r="G333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -7888,6 +8227,7 @@
       <c r="F334" t="n">
         <v>8</v>
       </c>
+      <c r="G334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -7910,6 +8250,7 @@
       <c r="F335" t="n">
         <v>8</v>
       </c>
+      <c r="G335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -7932,6 +8273,7 @@
       <c r="F336" t="n">
         <v>8</v>
       </c>
+      <c r="G336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -7954,6 +8296,7 @@
       <c r="F337" t="n">
         <v>8</v>
       </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7976,6 +8319,7 @@
       <c r="F338" t="n">
         <v>8</v>
       </c>
+      <c r="G338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -7998,6 +8342,7 @@
       <c r="F339" t="n">
         <v>8</v>
       </c>
+      <c r="G339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -8020,6 +8365,7 @@
       <c r="F340" t="n">
         <v>8</v>
       </c>
+      <c r="G340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -8042,6 +8388,7 @@
       <c r="F341" t="n">
         <v>8</v>
       </c>
+      <c r="G341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -8064,6 +8411,7 @@
       <c r="F342" t="n">
         <v>8</v>
       </c>
+      <c r="G342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -8086,6 +8434,7 @@
       <c r="F343" t="n">
         <v>8</v>
       </c>
+      <c r="G343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -8108,6 +8457,7 @@
       <c r="F344" t="n">
         <v>8</v>
       </c>
+      <c r="G344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -8130,6 +8480,7 @@
       <c r="F345" t="n">
         <v>8</v>
       </c>
+      <c r="G345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -8152,6 +8503,7 @@
       <c r="F346" t="n">
         <v>8</v>
       </c>
+      <c r="G346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -8174,6 +8526,7 @@
       <c r="F347" t="n">
         <v>8</v>
       </c>
+      <c r="G347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -8196,6 +8549,7 @@
       <c r="F348" t="n">
         <v>8</v>
       </c>
+      <c r="G348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -8218,6 +8572,7 @@
       <c r="F349" t="n">
         <v>8</v>
       </c>
+      <c r="G349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -8240,6 +8595,7 @@
       <c r="F350" t="n">
         <v>8</v>
       </c>
+      <c r="G350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -8262,6 +8618,7 @@
       <c r="F351" t="n">
         <v>8</v>
       </c>
+      <c r="G351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -8284,6 +8641,7 @@
       <c r="F352" t="n">
         <v>8</v>
       </c>
+      <c r="G352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -8306,6 +8664,7 @@
       <c r="F353" t="n">
         <v>8</v>
       </c>
+      <c r="G353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -8328,6 +8687,7 @@
       <c r="F354" t="n">
         <v>8</v>
       </c>
+      <c r="G354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -8350,6 +8710,7 @@
       <c r="F355" t="n">
         <v>8</v>
       </c>
+      <c r="G355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -8372,6 +8733,7 @@
       <c r="F356" t="n">
         <v>8</v>
       </c>
+      <c r="G356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -8394,6 +8756,7 @@
       <c r="F357" t="n">
         <v>8</v>
       </c>
+      <c r="G357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -8416,6 +8779,7 @@
       <c r="F358" t="n">
         <v>8</v>
       </c>
+      <c r="G358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -8438,6 +8802,7 @@
       <c r="F359" t="n">
         <v>8</v>
       </c>
+      <c r="G359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -8460,6 +8825,7 @@
       <c r="F360" t="n">
         <v>8</v>
       </c>
+      <c r="G360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -8482,6 +8848,7 @@
       <c r="F361" t="n">
         <v>8</v>
       </c>
+      <c r="G361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -8504,6 +8871,7 @@
       <c r="F362" t="n">
         <v>8</v>
       </c>
+      <c r="G362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -8526,6 +8894,7 @@
       <c r="F363" t="n">
         <v>8</v>
       </c>
+      <c r="G363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -8548,6 +8917,7 @@
       <c r="F364" t="n">
         <v>8</v>
       </c>
+      <c r="G364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -8570,6 +8940,7 @@
       <c r="F365" t="n">
         <v>8</v>
       </c>
+      <c r="G365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -8592,6 +8963,7 @@
       <c r="F366" t="n">
         <v>8</v>
       </c>
+      <c r="G366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -8614,6 +8986,7 @@
       <c r="F367" t="n">
         <v>8</v>
       </c>
+      <c r="G367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -8636,6 +9009,7 @@
       <c r="F368" t="n">
         <v>8</v>
       </c>
+      <c r="G368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -8658,6 +9032,7 @@
       <c r="F369" t="n">
         <v>8</v>
       </c>
+      <c r="G369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -8680,6 +9055,7 @@
       <c r="F370" t="n">
         <v>8</v>
       </c>
+      <c r="G370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -8702,6 +9078,7 @@
       <c r="F371" t="n">
         <v>8</v>
       </c>
+      <c r="G371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -8724,6 +9101,7 @@
       <c r="F372" t="n">
         <v>8</v>
       </c>
+      <c r="G372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -8746,6 +9124,7 @@
       <c r="F373" t="n">
         <v>8</v>
       </c>
+      <c r="G373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -8768,6 +9147,7 @@
       <c r="F374" t="n">
         <v>8</v>
       </c>
+      <c r="G374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -8790,6 +9170,7 @@
       <c r="F375" t="n">
         <v>8</v>
       </c>
+      <c r="G375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -8812,6 +9193,7 @@
       <c r="F376" t="n">
         <v>8</v>
       </c>
+      <c r="G376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -8834,6 +9216,7 @@
       <c r="F377" t="n">
         <v>8</v>
       </c>
+      <c r="G377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -8856,6 +9239,7 @@
       <c r="F378" t="n">
         <v>8</v>
       </c>
+      <c r="G378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -8878,6 +9262,7 @@
       <c r="F379" t="n">
         <v>8</v>
       </c>
+      <c r="G379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -8900,6 +9285,7 @@
       <c r="F380" t="n">
         <v>8</v>
       </c>
+      <c r="G380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -8922,6 +9308,7 @@
       <c r="F381" t="n">
         <v>8</v>
       </c>
+      <c r="G381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -8944,6 +9331,7 @@
       <c r="F382" t="n">
         <v>8</v>
       </c>
+      <c r="G382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -8966,6 +9354,7 @@
       <c r="F383" t="n">
         <v>8</v>
       </c>
+      <c r="G383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -8988,6 +9377,7 @@
       <c r="F384" t="n">
         <v>8</v>
       </c>
+      <c r="G384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -9010,6 +9400,7 @@
       <c r="F385" t="n">
         <v>8</v>
       </c>
+      <c r="G385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -9032,6 +9423,7 @@
       <c r="F386" t="n">
         <v>8</v>
       </c>
+      <c r="G386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -9054,6 +9446,7 @@
       <c r="F387" t="n">
         <v>8</v>
       </c>
+      <c r="G387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -9076,6 +9469,7 @@
       <c r="F388" t="n">
         <v>8</v>
       </c>
+      <c r="G388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -9098,6 +9492,7 @@
       <c r="F389" t="n">
         <v>8</v>
       </c>
+      <c r="G389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -9120,6 +9515,7 @@
       <c r="F390" t="n">
         <v>8</v>
       </c>
+      <c r="G390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -9142,6 +9538,7 @@
       <c r="F391" t="n">
         <v>8</v>
       </c>
+      <c r="G391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -9164,6 +9561,7 @@
       <c r="F392" t="n">
         <v>8</v>
       </c>
+      <c r="G392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -9186,6 +9584,7 @@
       <c r="F393" t="n">
         <v>8</v>
       </c>
+      <c r="G393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -9208,6 +9607,7 @@
       <c r="F394" t="n">
         <v>8</v>
       </c>
+      <c r="G394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -9230,6 +9630,7 @@
       <c r="F395" t="n">
         <v>8</v>
       </c>
+      <c r="G395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -9252,6 +9653,7 @@
       <c r="F396" t="n">
         <v>8</v>
       </c>
+      <c r="G396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -9274,6 +9676,7 @@
       <c r="F397" t="n">
         <v>8</v>
       </c>
+      <c r="G397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -9296,6 +9699,7 @@
       <c r="F398" t="n">
         <v>8</v>
       </c>
+      <c r="G398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -9318,6 +9722,7 @@
       <c r="F399" t="n">
         <v>8</v>
       </c>
+      <c r="G399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -9340,6 +9745,7 @@
       <c r="F400" t="n">
         <v>8</v>
       </c>
+      <c r="G400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -9362,6 +9768,7 @@
       <c r="F401" t="n">
         <v>8</v>
       </c>
+      <c r="G401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -9384,6 +9791,7 @@
       <c r="F402" t="n">
         <v>8</v>
       </c>
+      <c r="G402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -9406,6 +9814,7 @@
       <c r="F403" t="n">
         <v>8</v>
       </c>
+      <c r="G403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -9428,6 +9837,7 @@
       <c r="F404" t="n">
         <v>8</v>
       </c>
+      <c r="G404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -9450,6 +9860,7 @@
       <c r="F405" t="n">
         <v>8</v>
       </c>
+      <c r="G405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -9472,6 +9883,7 @@
       <c r="F406" t="n">
         <v>8</v>
       </c>
+      <c r="G406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -9494,6 +9906,7 @@
       <c r="F407" t="n">
         <v>8</v>
       </c>
+      <c r="G407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -9516,6 +9929,7 @@
       <c r="F408" t="n">
         <v>8</v>
       </c>
+      <c r="G408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -9538,6 +9952,7 @@
       <c r="F409" t="n">
         <v>8</v>
       </c>
+      <c r="G409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -9560,6 +9975,7 @@
       <c r="F410" t="n">
         <v>8</v>
       </c>
+      <c r="G410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -9582,6 +9998,7 @@
       <c r="F411" t="n">
         <v>8</v>
       </c>
+      <c r="G411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -9604,6 +10021,7 @@
       <c r="F412" t="n">
         <v>8</v>
       </c>
+      <c r="G412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -9626,6 +10044,7 @@
       <c r="F413" t="n">
         <v>8</v>
       </c>
+      <c r="G413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -9648,6 +10067,7 @@
       <c r="F414" t="n">
         <v>8</v>
       </c>
+      <c r="G414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -9670,6 +10090,7 @@
       <c r="F415" t="n">
         <v>8</v>
       </c>
+      <c r="G415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -9692,6 +10113,7 @@
       <c r="F416" t="n">
         <v>8</v>
       </c>
+      <c r="G416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -9714,6 +10136,7 @@
       <c r="F417" t="n">
         <v>8</v>
       </c>
+      <c r="G417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -9736,6 +10159,7 @@
       <c r="F418" t="n">
         <v>8</v>
       </c>
+      <c r="G418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -9758,6 +10182,7 @@
       <c r="F419" t="n">
         <v>8</v>
       </c>
+      <c r="G419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -9780,6 +10205,7 @@
       <c r="F420" t="n">
         <v>8</v>
       </c>
+      <c r="G420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -9802,6 +10228,7 @@
       <c r="F421" t="n">
         <v>8</v>
       </c>
+      <c r="G421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -9824,6 +10251,7 @@
       <c r="F422" t="n">
         <v>8</v>
       </c>
+      <c r="G422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -9846,6 +10274,7 @@
       <c r="F423" t="n">
         <v>8</v>
       </c>
+      <c r="G423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -9868,6 +10297,7 @@
       <c r="F424" t="n">
         <v>8</v>
       </c>
+      <c r="G424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -9890,6 +10320,7 @@
       <c r="F425" t="n">
         <v>8</v>
       </c>
+      <c r="G425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -9912,6 +10343,7 @@
       <c r="F426" t="n">
         <v>8</v>
       </c>
+      <c r="G426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -9934,6 +10366,7 @@
       <c r="F427" t="n">
         <v>8</v>
       </c>
+      <c r="G427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -9956,6 +10389,7 @@
       <c r="F428" t="n">
         <v>8</v>
       </c>
+      <c r="G428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -9978,6 +10412,7 @@
       <c r="F429" t="n">
         <v>8</v>
       </c>
+      <c r="G429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -10000,6 +10435,7 @@
       <c r="F430" t="n">
         <v>8</v>
       </c>
+      <c r="G430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -10022,6 +10458,7 @@
       <c r="F431" t="n">
         <v>8</v>
       </c>
+      <c r="G431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -10044,6 +10481,7 @@
       <c r="F432" t="n">
         <v>8</v>
       </c>
+      <c r="G432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -10066,6 +10504,7 @@
       <c r="F433" t="n">
         <v>8</v>
       </c>
+      <c r="G433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -10088,6 +10527,7 @@
       <c r="F434" t="n">
         <v>8</v>
       </c>
+      <c r="G434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -10110,6 +10550,7 @@
       <c r="F435" t="n">
         <v>8</v>
       </c>
+      <c r="G435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -10132,6 +10573,7 @@
       <c r="F436" t="n">
         <v>8</v>
       </c>
+      <c r="G436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -10154,6 +10596,7 @@
       <c r="F437" t="n">
         <v>8</v>
       </c>
+      <c r="G437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -10176,6 +10619,7 @@
       <c r="F438" t="n">
         <v>8</v>
       </c>
+      <c r="G438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -10198,6 +10642,7 @@
       <c r="F439" t="n">
         <v>8</v>
       </c>
+      <c r="G439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -10220,6 +10665,7 @@
       <c r="F440" t="n">
         <v>8</v>
       </c>
+      <c r="G440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -10242,6 +10688,7 @@
       <c r="F441" t="n">
         <v>8</v>
       </c>
+      <c r="G441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -10264,6 +10711,7 @@
       <c r="F442" t="n">
         <v>8</v>
       </c>
+      <c r="G442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -10286,6 +10734,7 @@
       <c r="F443" t="n">
         <v>8</v>
       </c>
+      <c r="G443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -10308,6 +10757,7 @@
       <c r="F444" t="n">
         <v>8</v>
       </c>
+      <c r="G444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -10330,6 +10780,7 @@
       <c r="F445" t="n">
         <v>8</v>
       </c>
+      <c r="G445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -10352,6 +10803,7 @@
       <c r="F446" t="n">
         <v>8</v>
       </c>
+      <c r="G446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -10374,6 +10826,7 @@
       <c r="F447" t="n">
         <v>8</v>
       </c>
+      <c r="G447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -10396,6 +10849,7 @@
       <c r="F448" t="n">
         <v>8</v>
       </c>
+      <c r="G448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -10418,6 +10872,7 @@
       <c r="F449" t="n">
         <v>8</v>
       </c>
+      <c r="G449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -10440,6 +10895,7 @@
       <c r="F450" t="n">
         <v>8</v>
       </c>
+      <c r="G450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -10462,6 +10918,7 @@
       <c r="F451" t="n">
         <v>8</v>
       </c>
+      <c r="G451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -10484,6 +10941,7 @@
       <c r="F452" t="n">
         <v>8</v>
       </c>
+      <c r="G452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -10506,6 +10964,7 @@
       <c r="F453" t="n">
         <v>8</v>
       </c>
+      <c r="G453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -10528,6 +10987,7 @@
       <c r="F454" t="n">
         <v>8</v>
       </c>
+      <c r="G454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -10550,6 +11010,7 @@
       <c r="F455" t="n">
         <v>8</v>
       </c>
+      <c r="G455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -10572,6 +11033,7 @@
       <c r="F456" t="n">
         <v>8</v>
       </c>
+      <c r="G456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -10594,6 +11056,7 @@
       <c r="F457" t="n">
         <v>8</v>
       </c>
+      <c r="G457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -10616,6 +11079,7 @@
       <c r="F458" t="n">
         <v>8</v>
       </c>
+      <c r="G458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -10638,6 +11102,7 @@
       <c r="F459" t="n">
         <v>8</v>
       </c>
+      <c r="G459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -10660,6 +11125,7 @@
       <c r="F460" t="n">
         <v>8</v>
       </c>
+      <c r="G460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -10682,6 +11148,7 @@
       <c r="F461" t="n">
         <v>8</v>
       </c>
+      <c r="G461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -10704,6 +11171,7 @@
       <c r="F462" t="n">
         <v>8</v>
       </c>
+      <c r="G462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -10726,6 +11194,7 @@
       <c r="F463" t="n">
         <v>8</v>
       </c>
+      <c r="G463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -10748,6 +11217,7 @@
       <c r="F464" t="n">
         <v>8</v>
       </c>
+      <c r="G464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -10770,6 +11240,7 @@
       <c r="F465" t="n">
         <v>8</v>
       </c>
+      <c r="G465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -10792,6 +11263,7 @@
       <c r="F466" t="n">
         <v>8</v>
       </c>
+      <c r="G466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -10814,6 +11286,7 @@
       <c r="F467" t="n">
         <v>8</v>
       </c>
+      <c r="G467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -10836,6 +11309,7 @@
       <c r="F468" t="n">
         <v>8</v>
       </c>
+      <c r="G468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -10858,6 +11332,7 @@
       <c r="F469" t="n">
         <v>8</v>
       </c>
+      <c r="G469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -10880,6 +11355,7 @@
       <c r="F470" t="n">
         <v>8</v>
       </c>
+      <c r="G470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -10902,6 +11378,7 @@
       <c r="F471" t="n">
         <v>8</v>
       </c>
+      <c r="G471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -10924,6 +11401,7 @@
       <c r="F472" t="n">
         <v>8</v>
       </c>
+      <c r="G472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -10946,6 +11424,7 @@
       <c r="F473" t="n">
         <v>8</v>
       </c>
+      <c r="G473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -10968,6 +11447,7 @@
       <c r="F474" t="n">
         <v>8</v>
       </c>
+      <c r="G474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -10990,6 +11470,7 @@
       <c r="F475" t="n">
         <v>8</v>
       </c>
+      <c r="G475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -11012,6 +11493,7 @@
       <c r="F476" t="n">
         <v>8</v>
       </c>
+      <c r="G476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -11034,6 +11516,7 @@
       <c r="F477" t="n">
         <v>8</v>
       </c>
+      <c r="G477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -11056,6 +11539,7 @@
       <c r="F478" t="n">
         <v>8</v>
       </c>
+      <c r="G478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -11078,6 +11562,7 @@
       <c r="F479" t="n">
         <v>8</v>
       </c>
+      <c r="G479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -11100,6 +11585,7 @@
       <c r="F480" t="n">
         <v>8</v>
       </c>
+      <c r="G480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -11122,6 +11608,7 @@
       <c r="F481" t="n">
         <v>8</v>
       </c>
+      <c r="G481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -11144,6 +11631,7 @@
       <c r="F482" t="n">
         <v>8</v>
       </c>
+      <c r="G482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -11166,6 +11654,7 @@
       <c r="F483" t="n">
         <v>8</v>
       </c>
+      <c r="G483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -11188,6 +11677,7 @@
       <c r="F484" t="n">
         <v>8</v>
       </c>
+      <c r="G484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -11210,6 +11700,7 @@
       <c r="F485" t="n">
         <v>8</v>
       </c>
+      <c r="G485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -11232,6 +11723,7 @@
       <c r="F486" t="n">
         <v>8</v>
       </c>
+      <c r="G486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -11254,6 +11746,7 @@
       <c r="F487" t="n">
         <v>8</v>
       </c>
+      <c r="G487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -11276,6 +11769,7 @@
       <c r="F488" t="n">
         <v>8</v>
       </c>
+      <c r="G488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -11298,6 +11792,7 @@
       <c r="F489" t="n">
         <v>8</v>
       </c>
+      <c r="G489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -11320,6 +11815,7 @@
       <c r="F490" t="n">
         <v>8</v>
       </c>
+      <c r="G490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -11342,6 +11838,7 @@
       <c r="F491" t="n">
         <v>8</v>
       </c>
+      <c r="G491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -11364,6 +11861,7 @@
       <c r="F492" t="n">
         <v>8</v>
       </c>
+      <c r="G492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -11386,6 +11884,7 @@
       <c r="F493" t="n">
         <v>8</v>
       </c>
+      <c r="G493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -11408,6 +11907,7 @@
       <c r="F494" t="n">
         <v>8</v>
       </c>
+      <c r="G494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -11430,6 +11930,7 @@
       <c r="F495" t="n">
         <v>8</v>
       </c>
+      <c r="G495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -11452,6 +11953,7 @@
       <c r="F496" t="n">
         <v>8</v>
       </c>
+      <c r="G496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -11474,6 +11976,7 @@
       <c r="F497" t="n">
         <v>8</v>
       </c>
+      <c r="G497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -11496,6 +11999,7 @@
       <c r="F498" t="n">
         <v>8</v>
       </c>
+      <c r="G498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -11518,6 +12022,7 @@
       <c r="F499" t="n">
         <v>8</v>
       </c>
+      <c r="G499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -11540,6 +12045,7 @@
       <c r="F500" t="n">
         <v>8</v>
       </c>
+      <c r="G500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -11562,6 +12068,7 @@
       <c r="F501" t="n">
         <v>8</v>
       </c>
+      <c r="G501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -11584,6 +12091,7 @@
       <c r="F502" t="n">
         <v>8</v>
       </c>
+      <c r="G502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -11606,6 +12114,7 @@
       <c r="F503" t="n">
         <v>8</v>
       </c>
+      <c r="G503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -11628,6 +12137,7 @@
       <c r="F504" t="n">
         <v>8</v>
       </c>
+      <c r="G504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -11650,6 +12160,7 @@
       <c r="F505" t="n">
         <v>8</v>
       </c>
+      <c r="G505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -11672,6 +12183,7 @@
       <c r="F506" t="n">
         <v>8</v>
       </c>
+      <c r="G506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -11694,6 +12206,7 @@
       <c r="F507" t="n">
         <v>8</v>
       </c>
+      <c r="G507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -11716,6 +12229,7 @@
       <c r="F508" t="n">
         <v>8</v>
       </c>
+      <c r="G508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -11738,6 +12252,7 @@
       <c r="F509" t="n">
         <v>8</v>
       </c>
+      <c r="G509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -11760,6 +12275,7 @@
       <c r="F510" t="n">
         <v>8</v>
       </c>
+      <c r="G510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -11782,6 +12298,7 @@
       <c r="F511" t="n">
         <v>8</v>
       </c>
+      <c r="G511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -11804,6 +12321,7 @@
       <c r="F512" t="n">
         <v>8</v>
       </c>
+      <c r="G512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -11826,6 +12344,7 @@
       <c r="F513" t="n">
         <v>8</v>
       </c>
+      <c r="G513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -11848,6 +12367,7 @@
       <c r="F514" t="n">
         <v>8</v>
       </c>
+      <c r="G514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -11870,6 +12390,7 @@
       <c r="F515" t="n">
         <v>8</v>
       </c>
+      <c r="G515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -11892,6 +12413,7 @@
       <c r="F516" t="n">
         <v>8</v>
       </c>
+      <c r="G516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -11914,6 +12436,7 @@
       <c r="F517" t="n">
         <v>8</v>
       </c>
+      <c r="G517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -11936,6 +12459,7 @@
       <c r="F518" t="n">
         <v>8</v>
       </c>
+      <c r="G518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -11958,6 +12482,7 @@
       <c r="F519" t="n">
         <v>8</v>
       </c>
+      <c r="G519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -11980,6 +12505,7 @@
       <c r="F520" t="n">
         <v>8</v>
       </c>
+      <c r="G520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -12002,6 +12528,7 @@
       <c r="F521" t="n">
         <v>8</v>
       </c>
+      <c r="G521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -12024,6 +12551,7 @@
       <c r="F522" t="n">
         <v>8</v>
       </c>
+      <c r="G522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -12046,6 +12574,7 @@
       <c r="F523" t="n">
         <v>8</v>
       </c>
+      <c r="G523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -12068,6 +12597,7 @@
       <c r="F524" t="n">
         <v>8</v>
       </c>
+      <c r="G524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -12090,6 +12620,7 @@
       <c r="F525" t="n">
         <v>8</v>
       </c>
+      <c r="G525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -12112,6 +12643,7 @@
       <c r="F526" t="n">
         <v>8</v>
       </c>
+      <c r="G526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -12134,6 +12666,7 @@
       <c r="F527" t="n">
         <v>8</v>
       </c>
+      <c r="G527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -12156,6 +12689,7 @@
       <c r="F528" t="n">
         <v>8</v>
       </c>
+      <c r="G528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -12178,6 +12712,7 @@
       <c r="F529" t="n">
         <v>8</v>
       </c>
+      <c r="G529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -12200,6 +12735,7 @@
       <c r="F530" t="n">
         <v>8</v>
       </c>
+      <c r="G530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -12222,6 +12758,7 @@
       <c r="F531" t="n">
         <v>8</v>
       </c>
+      <c r="G531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -12244,6 +12781,7 @@
       <c r="F532" t="n">
         <v>8</v>
       </c>
+      <c r="G532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -12266,6 +12804,7 @@
       <c r="F533" t="n">
         <v>8</v>
       </c>
+      <c r="G533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -12288,6 +12827,7 @@
       <c r="F534" t="n">
         <v>8</v>
       </c>
+      <c r="G534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -12310,6 +12850,7 @@
       <c r="F535" t="n">
         <v>8</v>
       </c>
+      <c r="G535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -12332,6 +12873,7 @@
       <c r="F536" t="n">
         <v>8</v>
       </c>
+      <c r="G536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -12354,6 +12896,7 @@
       <c r="F537" t="n">
         <v>8</v>
       </c>
+      <c r="G537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -12376,6 +12919,7 @@
       <c r="F538" t="n">
         <v>8</v>
       </c>
+      <c r="G538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -12398,6 +12942,7 @@
       <c r="F539" t="n">
         <v>8</v>
       </c>
+      <c r="G539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -12420,6 +12965,7 @@
       <c r="F540" t="n">
         <v>8</v>
       </c>
+      <c r="G540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -12442,6 +12988,7 @@
       <c r="F541" t="n">
         <v>8</v>
       </c>
+      <c r="G541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -12464,6 +13011,7 @@
       <c r="F542" t="n">
         <v>8</v>
       </c>
+      <c r="G542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -12486,6 +13034,7 @@
       <c r="F543" t="n">
         <v>8</v>
       </c>
+      <c r="G543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -12508,6 +13057,7 @@
       <c r="F544" t="n">
         <v>8</v>
       </c>
+      <c r="G544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -12530,6 +13080,7 @@
       <c r="F545" t="n">
         <v>8</v>
       </c>
+      <c r="G545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -12552,6 +13103,7 @@
       <c r="F546" t="n">
         <v>8</v>
       </c>
+      <c r="G546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -12574,6 +13126,7 @@
       <c r="F547" t="n">
         <v>8</v>
       </c>
+      <c r="G547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -12596,6 +13149,7 @@
       <c r="F548" t="n">
         <v>8</v>
       </c>
+      <c r="G548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -12618,6 +13172,7 @@
       <c r="F549" t="n">
         <v>8</v>
       </c>
+      <c r="G549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -12640,6 +13195,7 @@
       <c r="F550" t="n">
         <v>8</v>
       </c>
+      <c r="G550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -12662,6 +13218,7 @@
       <c r="F551" t="n">
         <v>8</v>
       </c>
+      <c r="G551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -12684,6 +13241,7 @@
       <c r="F552" t="n">
         <v>8</v>
       </c>
+      <c r="G552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -12706,6 +13264,7 @@
       <c r="F553" t="n">
         <v>8</v>
       </c>
+      <c r="G553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -12728,6 +13287,7 @@
       <c r="F554" t="n">
         <v>8</v>
       </c>
+      <c r="G554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -12750,6 +13310,7 @@
       <c r="F555" t="n">
         <v>8</v>
       </c>
+      <c r="G555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="n">
@@ -12772,6 +13333,7 @@
       <c r="F556" t="n">
         <v>8</v>
       </c>
+      <c r="G556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -12794,6 +13356,7 @@
       <c r="F557" t="n">
         <v>8</v>
       </c>
+      <c r="G557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -12816,6 +13379,7 @@
       <c r="F558" t="n">
         <v>8</v>
       </c>
+      <c r="G558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
@@ -12838,6 +13402,7 @@
       <c r="F559" t="n">
         <v>8</v>
       </c>
+      <c r="G559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -12860,6 +13425,7 @@
       <c r="F560" t="n">
         <v>8</v>
       </c>
+      <c r="G560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -12882,6 +13448,7 @@
       <c r="F561" t="n">
         <v>8</v>
       </c>
+      <c r="G561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -12904,6 +13471,7 @@
       <c r="F562" t="n">
         <v>8</v>
       </c>
+      <c r="G562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -12926,6 +13494,7 @@
       <c r="F563" t="n">
         <v>8</v>
       </c>
+      <c r="G563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -12948,6 +13517,7 @@
       <c r="F564" t="n">
         <v>8</v>
       </c>
+      <c r="G564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -12970,6 +13540,7 @@
       <c r="F565" t="n">
         <v>8</v>
       </c>
+      <c r="G565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -12992,6 +13563,7 @@
       <c r="F566" t="n">
         <v>8</v>
       </c>
+      <c r="G566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -13014,6 +13586,7 @@
       <c r="F567" t="n">
         <v>8</v>
       </c>
+      <c r="G567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -13036,6 +13609,7 @@
       <c r="F568" t="n">
         <v>8</v>
       </c>
+      <c r="G568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -13058,6 +13632,7 @@
       <c r="F569" t="n">
         <v>8</v>
       </c>
+      <c r="G569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -13080,6 +13655,7 @@
       <c r="F570" t="n">
         <v>8</v>
       </c>
+      <c r="G570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -13102,6 +13678,7 @@
       <c r="F571" t="n">
         <v>8</v>
       </c>
+      <c r="G571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -13124,6 +13701,7 @@
       <c r="F572" t="n">
         <v>8</v>
       </c>
+      <c r="G572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -13146,6 +13724,7 @@
       <c r="F573" t="n">
         <v>8</v>
       </c>
+      <c r="G573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -13168,6 +13747,7 @@
       <c r="F574" t="n">
         <v>8</v>
       </c>
+      <c r="G574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -13190,6 +13770,7 @@
       <c r="F575" t="n">
         <v>8</v>
       </c>
+      <c r="G575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -13212,6 +13793,7 @@
       <c r="F576" t="n">
         <v>8</v>
       </c>
+      <c r="G576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -13234,6 +13816,7 @@
       <c r="F577" t="n">
         <v>8</v>
       </c>
+      <c r="G577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -13256,6 +13839,7 @@
       <c r="F578" t="n">
         <v>8</v>
       </c>
+      <c r="G578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -13278,6 +13862,7 @@
       <c r="F579" t="n">
         <v>8</v>
       </c>
+      <c r="G579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -13300,6 +13885,7 @@
       <c r="F580" t="n">
         <v>8</v>
       </c>
+      <c r="G580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -13322,6 +13908,7 @@
       <c r="F581" t="n">
         <v>8</v>
       </c>
+      <c r="G581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -13344,6 +13931,7 @@
       <c r="F582" t="n">
         <v>8</v>
       </c>
+      <c r="G582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -13366,6 +13954,7 @@
       <c r="F583" t="n">
         <v>8</v>
       </c>
+      <c r="G583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -13388,6 +13977,7 @@
       <c r="F584" t="n">
         <v>8</v>
       </c>
+      <c r="G584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -13410,6 +14000,7 @@
       <c r="F585" t="n">
         <v>8</v>
       </c>
+      <c r="G585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -13432,6 +14023,7 @@
       <c r="F586" t="n">
         <v>8</v>
       </c>
+      <c r="G586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -13454,6 +14046,7 @@
       <c r="F587" t="n">
         <v>8</v>
       </c>
+      <c r="G587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -13476,6 +14069,7 @@
       <c r="F588" t="n">
         <v>8</v>
       </c>
+      <c r="G588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -13498,6 +14092,7 @@
       <c r="F589" t="n">
         <v>8</v>
       </c>
+      <c r="G589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -13520,6 +14115,7 @@
       <c r="F590" t="n">
         <v>8</v>
       </c>
+      <c r="G590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -13542,6 +14138,7 @@
       <c r="F591" t="n">
         <v>8</v>
       </c>
+      <c r="G591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -13564,6 +14161,7 @@
       <c r="F592" t="n">
         <v>8</v>
       </c>
+      <c r="G592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -13586,6 +14184,7 @@
       <c r="F593" t="n">
         <v>8</v>
       </c>
+      <c r="G593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
@@ -13608,6 +14207,7 @@
       <c r="F594" t="n">
         <v>8</v>
       </c>
+      <c r="G594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -13630,6 +14230,7 @@
       <c r="F595" t="n">
         <v>8</v>
       </c>
+      <c r="G595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -13652,6 +14253,7 @@
       <c r="F596" t="n">
         <v>8</v>
       </c>
+      <c r="G596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -13674,6 +14276,7 @@
       <c r="F597" t="n">
         <v>8</v>
       </c>
+      <c r="G597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -13696,6 +14299,7 @@
       <c r="F598" t="n">
         <v>8</v>
       </c>
+      <c r="G598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -13718,6 +14322,7 @@
       <c r="F599" t="n">
         <v>8</v>
       </c>
+      <c r="G599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -13740,6 +14345,7 @@
       <c r="F600" t="n">
         <v>8</v>
       </c>
+      <c r="G600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -13762,6 +14368,7 @@
       <c r="F601" t="n">
         <v>8</v>
       </c>
+      <c r="G601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -13784,6 +14391,7 @@
       <c r="F602" t="n">
         <v>8</v>
       </c>
+      <c r="G602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -13806,6 +14414,7 @@
       <c r="F603" t="n">
         <v>8</v>
       </c>
+      <c r="G603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -13828,6 +14437,7 @@
       <c r="F604" t="n">
         <v>8</v>
       </c>
+      <c r="G604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -13850,6 +14460,7 @@
       <c r="F605" t="n">
         <v>8</v>
       </c>
+      <c r="G605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -13872,6 +14483,7 @@
       <c r="F606" t="n">
         <v>8</v>
       </c>
+      <c r="G606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -13894,6 +14506,7 @@
       <c r="F607" t="n">
         <v>8</v>
       </c>
+      <c r="G607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -13916,6 +14529,7 @@
       <c r="F608" t="n">
         <v>8</v>
       </c>
+      <c r="G608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -13938,6 +14552,7 @@
       <c r="F609" t="n">
         <v>8</v>
       </c>
+      <c r="G609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -13960,6 +14575,7 @@
       <c r="F610" t="n">
         <v>8</v>
       </c>
+      <c r="G610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -13982,6 +14598,7 @@
       <c r="F611" t="n">
         <v>8</v>
       </c>
+      <c r="G611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -14004,6 +14621,7 @@
       <c r="F612" t="n">
         <v>8</v>
       </c>
+      <c r="G612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -14026,6 +14644,7 @@
       <c r="F613" t="n">
         <v>8</v>
       </c>
+      <c r="G613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -14048,6 +14667,7 @@
       <c r="F614" t="n">
         <v>8</v>
       </c>
+      <c r="G614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -14070,6 +14690,7 @@
       <c r="F615" t="n">
         <v>8</v>
       </c>
+      <c r="G615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -14092,6 +14713,7 @@
       <c r="F616" t="n">
         <v>8</v>
       </c>
+      <c r="G616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -14114,6 +14736,7 @@
       <c r="F617" t="n">
         <v>8</v>
       </c>
+      <c r="G617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -14136,6 +14759,7 @@
       <c r="F618" t="n">
         <v>8</v>
       </c>
+      <c r="G618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -14158,6 +14782,7 @@
       <c r="F619" t="n">
         <v>8</v>
       </c>
+      <c r="G619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -14180,6 +14805,7 @@
       <c r="F620" t="n">
         <v>8</v>
       </c>
+      <c r="G620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -14202,6 +14828,7 @@
       <c r="F621" t="n">
         <v>8</v>
       </c>
+      <c r="G621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -14224,6 +14851,7 @@
       <c r="F622" t="n">
         <v>8</v>
       </c>
+      <c r="G622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -14246,6 +14874,7 @@
       <c r="F623" t="n">
         <v>8</v>
       </c>
+      <c r="G623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -14268,6 +14897,7 @@
       <c r="F624" t="n">
         <v>8</v>
       </c>
+      <c r="G624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -14290,6 +14920,7 @@
       <c r="F625" t="n">
         <v>8</v>
       </c>
+      <c r="G625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -14312,6 +14943,7 @@
       <c r="F626" t="n">
         <v>8</v>
       </c>
+      <c r="G626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -14334,6 +14966,7 @@
       <c r="F627" t="n">
         <v>8</v>
       </c>
+      <c r="G627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -14356,6 +14989,7 @@
       <c r="F628" t="n">
         <v>8</v>
       </c>
+      <c r="G628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -14378,6 +15012,7 @@
       <c r="F629" t="n">
         <v>8</v>
       </c>
+      <c r="G629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -14400,6 +15035,7 @@
       <c r="F630" t="n">
         <v>8</v>
       </c>
+      <c r="G630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -14422,6 +15058,7 @@
       <c r="F631" t="n">
         <v>8</v>
       </c>
+      <c r="G631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -14444,6 +15081,7 @@
       <c r="F632" t="n">
         <v>8</v>
       </c>
+      <c r="G632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -14466,6 +15104,7 @@
       <c r="F633" t="n">
         <v>8</v>
       </c>
+      <c r="G633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -14488,6 +15127,7 @@
       <c r="F634" t="n">
         <v>8</v>
       </c>
+      <c r="G634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -14510,6 +15150,7 @@
       <c r="F635" t="n">
         <v>8</v>
       </c>
+      <c r="G635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -14532,6 +15173,7 @@
       <c r="F636" t="n">
         <v>8</v>
       </c>
+      <c r="G636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -14554,6 +15196,7 @@
       <c r="F637" t="n">
         <v>8</v>
       </c>
+      <c r="G637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -14576,6 +15219,7 @@
       <c r="F638" t="n">
         <v>8</v>
       </c>
+      <c r="G638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -14598,6 +15242,7 @@
       <c r="F639" t="n">
         <v>8</v>
       </c>
+      <c r="G639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -14620,6 +15265,7 @@
       <c r="F640" t="n">
         <v>8</v>
       </c>
+      <c r="G640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -14642,6 +15288,7 @@
       <c r="F641" t="n">
         <v>8</v>
       </c>
+      <c r="G641" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -14664,6 +15311,7 @@
       <c r="F642" t="n">
         <v>8</v>
       </c>
+      <c r="G642" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -14686,6 +15334,7 @@
       <c r="F643" t="n">
         <v>8</v>
       </c>
+      <c r="G643" t="inlineStr"/>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -14708,6 +15357,7 @@
       <c r="F644" t="n">
         <v>8</v>
       </c>
+      <c r="G644" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -14730,6 +15380,7 @@
       <c r="F645" t="n">
         <v>8</v>
       </c>
+      <c r="G645" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -14752,6 +15403,7 @@
       <c r="F646" t="n">
         <v>8</v>
       </c>
+      <c r="G646" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -14774,6 +15426,7 @@
       <c r="F647" t="n">
         <v>8</v>
       </c>
+      <c r="G647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -14796,6 +15449,7 @@
       <c r="F648" t="n">
         <v>8</v>
       </c>
+      <c r="G648" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -14818,6 +15472,7 @@
       <c r="F649" t="n">
         <v>8</v>
       </c>
+      <c r="G649" t="inlineStr"/>
     </row>
     <row r="650">
       <c r="A650" t="n">
@@ -14840,6 +15495,7 @@
       <c r="F650" t="n">
         <v>8</v>
       </c>
+      <c r="G650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -14862,6 +15518,7 @@
       <c r="F651" t="n">
         <v>8</v>
       </c>
+      <c r="G651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
@@ -14884,6 +15541,7 @@
       <c r="F652" t="n">
         <v>8</v>
       </c>
+      <c r="G652" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -14906,6 +15564,7 @@
       <c r="F653" t="n">
         <v>8</v>
       </c>
+      <c r="G653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -14928,6 +15587,7 @@
       <c r="F654" t="n">
         <v>8</v>
       </c>
+      <c r="G654" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -14950,6 +15610,7 @@
       <c r="F655" t="n">
         <v>8</v>
       </c>
+      <c r="G655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -14972,6 +15633,7 @@
       <c r="F656" t="n">
         <v>8</v>
       </c>
+      <c r="G656" t="inlineStr"/>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -14994,6 +15656,7 @@
       <c r="F657" t="n">
         <v>8</v>
       </c>
+      <c r="G657" t="inlineStr"/>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -15016,6 +15679,7 @@
       <c r="F658" t="n">
         <v>8</v>
       </c>
+      <c r="G658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -15038,6 +15702,7 @@
       <c r="F659" t="n">
         <v>8</v>
       </c>
+      <c r="G659" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" t="n">
@@ -15060,6 +15725,7 @@
       <c r="F660" t="n">
         <v>8</v>
       </c>
+      <c r="G660" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -15082,6 +15748,7 @@
       <c r="F661" t="n">
         <v>8</v>
       </c>
+      <c r="G661" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -15104,6 +15771,7 @@
       <c r="F662" t="n">
         <v>8</v>
       </c>
+      <c r="G662" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -15126,6 +15794,7 @@
       <c r="F663" t="n">
         <v>8</v>
       </c>
+      <c r="G663" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -15148,6 +15817,7 @@
       <c r="F664" t="n">
         <v>8</v>
       </c>
+      <c r="G664" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -15170,6 +15840,7 @@
       <c r="F665" t="n">
         <v>8</v>
       </c>
+      <c r="G665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -15192,6 +15863,7 @@
       <c r="F666" t="n">
         <v>8</v>
       </c>
+      <c r="G666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -15214,6 +15886,7 @@
       <c r="F667" t="n">
         <v>8</v>
       </c>
+      <c r="G667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -15236,6 +15909,7 @@
       <c r="F668" t="n">
         <v>8</v>
       </c>
+      <c r="G668" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -15258,6 +15932,7 @@
       <c r="F669" t="n">
         <v>8</v>
       </c>
+      <c r="G669" t="inlineStr"/>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -15280,6 +15955,7 @@
       <c r="F670" t="n">
         <v>8</v>
       </c>
+      <c r="G670" t="inlineStr"/>
     </row>
     <row r="671">
       <c r="A671" t="n">
@@ -15302,6 +15978,7 @@
       <c r="F671" t="n">
         <v>8</v>
       </c>
+      <c r="G671" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -15324,6 +16001,7 @@
       <c r="F672" t="n">
         <v>8</v>
       </c>
+      <c r="G672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -15346,6 +16024,7 @@
       <c r="F673" t="n">
         <v>8</v>
       </c>
+      <c r="G673" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -15368,6 +16047,7 @@
       <c r="F674" t="n">
         <v>8</v>
       </c>
+      <c r="G674" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -15390,6 +16070,7 @@
       <c r="F675" t="n">
         <v>8</v>
       </c>
+      <c r="G675" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -15412,6 +16093,7 @@
       <c r="F676" t="n">
         <v>8</v>
       </c>
+      <c r="G676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -15434,6 +16116,7 @@
       <c r="F677" t="n">
         <v>8</v>
       </c>
+      <c r="G677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -15456,6 +16139,7 @@
       <c r="F678" t="n">
         <v>8</v>
       </c>
+      <c r="G678" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -15478,6 +16162,7 @@
       <c r="F679" t="n">
         <v>8</v>
       </c>
+      <c r="G679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -15500,6 +16185,7 @@
       <c r="F680" t="n">
         <v>8</v>
       </c>
+      <c r="G680" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -15522,6 +16208,7 @@
       <c r="F681" t="n">
         <v>8</v>
       </c>
+      <c r="G681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -15544,6 +16231,7 @@
       <c r="F682" t="n">
         <v>8</v>
       </c>
+      <c r="G682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -15566,6 +16254,7 @@
       <c r="F683" t="n">
         <v>8</v>
       </c>
+      <c r="G683" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -15588,6 +16277,7 @@
       <c r="F684" t="n">
         <v>8</v>
       </c>
+      <c r="G684" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -15610,6 +16300,7 @@
       <c r="F685" t="n">
         <v>8</v>
       </c>
+      <c r="G685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -15632,6 +16323,7 @@
       <c r="F686" t="n">
         <v>8</v>
       </c>
+      <c r="G686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -15654,6 +16346,7 @@
       <c r="F687" t="n">
         <v>8</v>
       </c>
+      <c r="G687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -15676,6 +16369,7 @@
       <c r="F688" t="n">
         <v>8</v>
       </c>
+      <c r="G688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -15698,6 +16392,7 @@
       <c r="F689" t="n">
         <v>8</v>
       </c>
+      <c r="G689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -15720,6 +16415,7 @@
       <c r="F690" t="n">
         <v>8</v>
       </c>
+      <c r="G690" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" t="n">
@@ -15742,6 +16438,7 @@
       <c r="F691" t="n">
         <v>8</v>
       </c>
+      <c r="G691" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -15764,6 +16461,7 @@
       <c r="F692" t="n">
         <v>8</v>
       </c>
+      <c r="G692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -15786,6 +16484,7 @@
       <c r="F693" t="n">
         <v>8</v>
       </c>
+      <c r="G693" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -15808,6 +16507,7 @@
       <c r="F694" t="n">
         <v>8</v>
       </c>
+      <c r="G694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -15830,6 +16530,7 @@
       <c r="F695" t="n">
         <v>8</v>
       </c>
+      <c r="G695" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -15852,6 +16553,7 @@
       <c r="F696" t="n">
         <v>8</v>
       </c>
+      <c r="G696" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -15874,6 +16576,7 @@
       <c r="F697" t="n">
         <v>8</v>
       </c>
+      <c r="G697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -15896,6 +16599,7 @@
       <c r="F698" t="n">
         <v>8</v>
       </c>
+      <c r="G698" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -15918,6 +16622,7 @@
       <c r="F699" t="n">
         <v>8</v>
       </c>
+      <c r="G699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -15940,6 +16645,7 @@
       <c r="F700" t="n">
         <v>8</v>
       </c>
+      <c r="G700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -15962,6 +16668,7 @@
       <c r="F701" t="n">
         <v>8</v>
       </c>
+      <c r="G701" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -15984,6 +16691,7 @@
       <c r="F702" t="n">
         <v>8</v>
       </c>
+      <c r="G702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -16006,6 +16714,7 @@
       <c r="F703" t="n">
         <v>8</v>
       </c>
+      <c r="G703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -16028,6 +16737,7 @@
       <c r="F704" t="n">
         <v>8</v>
       </c>
+      <c r="G704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -16050,6 +16760,7 @@
       <c r="F705" t="n">
         <v>8</v>
       </c>
+      <c r="G705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -16072,6 +16783,7 @@
       <c r="F706" t="n">
         <v>8</v>
       </c>
+      <c r="G706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -16094,6 +16806,7 @@
       <c r="F707" t="n">
         <v>8</v>
       </c>
+      <c r="G707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -16116,6 +16829,7 @@
       <c r="F708" t="n">
         <v>8</v>
       </c>
+      <c r="G708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -16138,6 +16852,7 @@
       <c r="F709" t="n">
         <v>8</v>
       </c>
+      <c r="G709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -16160,6 +16875,7 @@
       <c r="F710" t="n">
         <v>8</v>
       </c>
+      <c r="G710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -16182,6 +16898,7 @@
       <c r="F711" t="n">
         <v>8</v>
       </c>
+      <c r="G711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -16204,6 +16921,7 @@
       <c r="F712" t="n">
         <v>8</v>
       </c>
+      <c r="G712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -16226,6 +16944,7 @@
       <c r="F713" t="n">
         <v>8</v>
       </c>
+      <c r="G713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -16248,6 +16967,7 @@
       <c r="F714" t="n">
         <v>8</v>
       </c>
+      <c r="G714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -16270,6 +16990,7 @@
       <c r="F715" t="n">
         <v>8</v>
       </c>
+      <c r="G715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -16292,6 +17013,7 @@
       <c r="F716" t="n">
         <v>8</v>
       </c>
+      <c r="G716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -16314,6 +17036,7 @@
       <c r="F717" t="n">
         <v>8</v>
       </c>
+      <c r="G717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -16336,6 +17059,7 @@
       <c r="F718" t="n">
         <v>8</v>
       </c>
+      <c r="G718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -16358,6 +17082,7 @@
       <c r="F719" t="n">
         <v>8</v>
       </c>
+      <c r="G719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -16380,6 +17105,7 @@
       <c r="F720" t="n">
         <v>8</v>
       </c>
+      <c r="G720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -16402,6 +17128,7 @@
       <c r="F721" t="n">
         <v>8</v>
       </c>
+      <c r="G721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -16424,6 +17151,7 @@
       <c r="F722" t="n">
         <v>8</v>
       </c>
+      <c r="G722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -16446,6 +17174,7 @@
       <c r="F723" t="n">
         <v>8</v>
       </c>
+      <c r="G723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -16468,6 +17197,7 @@
       <c r="F724" t="n">
         <v>8</v>
       </c>
+      <c r="G724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -16490,6 +17220,7 @@
       <c r="F725" t="n">
         <v>8</v>
       </c>
+      <c r="G725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -16512,6 +17243,7 @@
       <c r="F726" t="n">
         <v>8</v>
       </c>
+      <c r="G726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="n">
@@ -16534,6 +17266,7 @@
       <c r="F727" t="n">
         <v>8</v>
       </c>
+      <c r="G727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -16556,6 +17289,7 @@
       <c r="F728" t="n">
         <v>8</v>
       </c>
+      <c r="G728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="n">
@@ -16578,6 +17312,7 @@
       <c r="F729" t="n">
         <v>8</v>
       </c>
+      <c r="G729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="n">
@@ -16600,6 +17335,7 @@
       <c r="F730" t="n">
         <v>8</v>
       </c>
+      <c r="G730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="n">
@@ -16622,6 +17358,7 @@
       <c r="F731" t="n">
         <v>8</v>
       </c>
+      <c r="G731" t="inlineStr"/>
     </row>
     <row r="732">
       <c r="A732" t="n">
@@ -16644,6 +17381,7 @@
       <c r="F732" t="n">
         <v>8</v>
       </c>
+      <c r="G732" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" t="n">
@@ -16666,6 +17404,7 @@
       <c r="F733" t="n">
         <v>8</v>
       </c>
+      <c r="G733" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" t="n">
@@ -16688,6 +17427,7 @@
       <c r="F734" t="n">
         <v>8</v>
       </c>
+      <c r="G734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="n">
@@ -16710,6 +17450,7 @@
       <c r="F735" t="n">
         <v>8</v>
       </c>
+      <c r="G735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="n">
@@ -16732,6 +17473,7 @@
       <c r="F736" t="n">
         <v>8</v>
       </c>
+      <c r="G736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="n">
@@ -16754,6 +17496,7 @@
       <c r="F737" t="n">
         <v>8</v>
       </c>
+      <c r="G737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="n">
@@ -16776,6 +17519,7 @@
       <c r="F738" t="n">
         <v>8</v>
       </c>
+      <c r="G738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="n">
@@ -16798,6 +17542,7 @@
       <c r="F739" t="n">
         <v>8</v>
       </c>
+      <c r="G739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="n">
@@ -16820,6 +17565,7 @@
       <c r="F740" t="n">
         <v>8</v>
       </c>
+      <c r="G740" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" t="n">
@@ -16842,6 +17588,7 @@
       <c r="F741" t="n">
         <v>8</v>
       </c>
+      <c r="G741" t="inlineStr"/>
     </row>
     <row r="742">
       <c r="A742" t="n">
@@ -16864,6 +17611,7 @@
       <c r="F742" t="n">
         <v>8</v>
       </c>
+      <c r="G742" t="inlineStr"/>
     </row>
     <row r="743">
       <c r="A743" t="n">
@@ -16886,6 +17634,7 @@
       <c r="F743" t="n">
         <v>8</v>
       </c>
+      <c r="G743" t="inlineStr"/>
     </row>
     <row r="744">
       <c r="A744" t="n">
@@ -16908,6 +17657,7 @@
       <c r="F744" t="n">
         <v>8</v>
       </c>
+      <c r="G744" t="inlineStr"/>
     </row>
     <row r="745">
       <c r="A745" t="n">
@@ -16930,6 +17680,7 @@
       <c r="F745" t="n">
         <v>8</v>
       </c>
+      <c r="G745" t="inlineStr"/>
     </row>
     <row r="746">
       <c r="A746" t="n">
@@ -16952,6 +17703,7 @@
       <c r="F746" t="n">
         <v>8</v>
       </c>
+      <c r="G746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="n">
@@ -16974,6 +17726,7 @@
       <c r="F747" t="n">
         <v>8</v>
       </c>
+      <c r="G747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="n">
@@ -16996,6 +17749,7 @@
       <c r="F748" t="n">
         <v>8</v>
       </c>
+      <c r="G748" t="inlineStr"/>
     </row>
     <row r="749">
       <c r="A749" t="n">
@@ -17018,6 +17772,7 @@
       <c r="F749" t="n">
         <v>8</v>
       </c>
+      <c r="G749" t="inlineStr"/>
     </row>
     <row r="750">
       <c r="A750" t="n">
@@ -17040,6 +17795,7 @@
       <c r="F750" t="n">
         <v>8</v>
       </c>
+      <c r="G750" t="inlineStr"/>
     </row>
     <row r="751">
       <c r="A751" t="n">
@@ -17062,6 +17818,7 @@
       <c r="F751" t="n">
         <v>8</v>
       </c>
+      <c r="G751" t="inlineStr"/>
     </row>
     <row r="752">
       <c r="A752" t="n">
@@ -17084,6 +17841,7 @@
       <c r="F752" t="n">
         <v>8</v>
       </c>
+      <c r="G752" t="inlineStr"/>
     </row>
     <row r="753">
       <c r="A753" t="n">
@@ -17106,6 +17864,7 @@
       <c r="F753" t="n">
         <v>8</v>
       </c>
+      <c r="G753" t="inlineStr"/>
     </row>
     <row r="754">
       <c r="A754" t="n">
@@ -17128,6 +17887,7 @@
       <c r="F754" t="n">
         <v>8</v>
       </c>
+      <c r="G754" t="inlineStr"/>
     </row>
     <row r="755">
       <c r="A755" t="n">
@@ -17150,6 +17910,7 @@
       <c r="F755" t="n">
         <v>8</v>
       </c>
+      <c r="G755" t="inlineStr"/>
     </row>
     <row r="756">
       <c r="A756" t="n">
@@ -17172,6 +17933,7 @@
       <c r="F756" t="n">
         <v>8</v>
       </c>
+      <c r="G756" t="inlineStr"/>
     </row>
     <row r="757">
       <c r="A757" t="n">
@@ -17194,6 +17956,7 @@
       <c r="F757" t="n">
         <v>8</v>
       </c>
+      <c r="G757" t="inlineStr"/>
     </row>
     <row r="758">
       <c r="A758" t="n">
@@ -17216,6 +17979,7 @@
       <c r="F758" t="n">
         <v>8</v>
       </c>
+      <c r="G758" t="inlineStr"/>
     </row>
     <row r="759">
       <c r="A759" t="n">
@@ -17238,6 +18002,7 @@
       <c r="F759" t="n">
         <v>8</v>
       </c>
+      <c r="G759" t="inlineStr"/>
     </row>
     <row r="760">
       <c r="A760" t="n">
@@ -17260,6 +18025,7 @@
       <c r="F760" t="n">
         <v>8</v>
       </c>
+      <c r="G760" t="inlineStr"/>
     </row>
     <row r="761">
       <c r="A761" t="n">
@@ -17282,6 +18048,7 @@
       <c r="F761" t="n">
         <v>8</v>
       </c>
+      <c r="G761" t="inlineStr"/>
     </row>
     <row r="762">
       <c r="A762" t="n">
@@ -17304,6 +18071,7 @@
       <c r="F762" t="n">
         <v>8</v>
       </c>
+      <c r="G762" t="inlineStr"/>
     </row>
     <row r="763">
       <c r="A763" t="n">
@@ -17326,6 +18094,7 @@
       <c r="F763" t="n">
         <v>8</v>
       </c>
+      <c r="G763" t="inlineStr"/>
     </row>
     <row r="764">
       <c r="A764" t="n">
@@ -17348,6 +18117,7 @@
       <c r="F764" t="n">
         <v>8</v>
       </c>
+      <c r="G764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="n">
@@ -17370,6 +18140,7 @@
       <c r="F765" t="n">
         <v>8</v>
       </c>
+      <c r="G765" t="inlineStr"/>
     </row>
     <row r="766">
       <c r="A766" t="n">
@@ -17392,6 +18163,7 @@
       <c r="F766" t="n">
         <v>8</v>
       </c>
+      <c r="G766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="n">
@@ -17414,6 +18186,7 @@
       <c r="F767" t="n">
         <v>8</v>
       </c>
+      <c r="G767" t="inlineStr"/>
     </row>
     <row r="768">
       <c r="A768" t="n">
@@ -17436,6 +18209,7 @@
       <c r="F768" t="n">
         <v>8</v>
       </c>
+      <c r="G768" t="inlineStr"/>
     </row>
     <row r="769">
       <c r="A769" t="n">
@@ -17458,6 +18232,7 @@
       <c r="F769" t="n">
         <v>8</v>
       </c>
+      <c r="G769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -17480,6 +18255,7 @@
       <c r="F770" t="n">
         <v>8</v>
       </c>
+      <c r="G770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" t="n">
@@ -17502,6 +18278,7 @@
       <c r="F771" t="n">
         <v>8</v>
       </c>
+      <c r="G771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -17524,6 +18301,7 @@
       <c r="F772" t="n">
         <v>8</v>
       </c>
+      <c r="G772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -17546,6 +18324,7 @@
       <c r="F773" t="n">
         <v>8</v>
       </c>
+      <c r="G773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="n">
@@ -17568,6 +18347,7 @@
       <c r="F774" t="n">
         <v>8</v>
       </c>
+      <c r="G774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="n">
@@ -17590,6 +18370,7 @@
       <c r="F775" t="n">
         <v>8</v>
       </c>
+      <c r="G775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="n">
@@ -17612,6 +18393,7 @@
       <c r="F776" t="n">
         <v>8</v>
       </c>
+      <c r="G776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="n">
@@ -17634,6 +18416,7 @@
       <c r="F777" t="n">
         <v>8</v>
       </c>
+      <c r="G777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="n">
@@ -17656,6 +18439,7 @@
       <c r="F778" t="n">
         <v>8</v>
       </c>
+      <c r="G778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="n">
@@ -17678,6 +18462,7 @@
       <c r="F779" t="n">
         <v>8</v>
       </c>
+      <c r="G779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -17700,6 +18485,7 @@
       <c r="F780" t="n">
         <v>8</v>
       </c>
+      <c r="G780" t="inlineStr"/>
     </row>
     <row r="781">
       <c r="A781" t="n">
@@ -17722,6 +18508,7 @@
       <c r="F781" t="n">
         <v>8</v>
       </c>
+      <c r="G781" t="inlineStr"/>
     </row>
     <row r="782">
       <c r="A782" t="n">
@@ -17744,6 +18531,7 @@
       <c r="F782" t="n">
         <v>8</v>
       </c>
+      <c r="G782" t="inlineStr"/>
     </row>
     <row r="783">
       <c r="A783" t="n">
@@ -17766,6 +18554,7 @@
       <c r="F783" t="n">
         <v>8</v>
       </c>
+      <c r="G783" t="inlineStr"/>
     </row>
     <row r="784">
       <c r="A784" t="n">
@@ -17788,6 +18577,7 @@
       <c r="F784" t="n">
         <v>8</v>
       </c>
+      <c r="G784" t="inlineStr"/>
     </row>
     <row r="785">
       <c r="A785" t="n">
@@ -17810,6 +18600,7 @@
       <c r="F785" t="n">
         <v>8</v>
       </c>
+      <c r="G785" t="inlineStr"/>
     </row>
     <row r="786">
       <c r="A786" t="n">
@@ -17832,6 +18623,7 @@
       <c r="F786" t="n">
         <v>8</v>
       </c>
+      <c r="G786" t="inlineStr"/>
     </row>
     <row r="787">
       <c r="A787" t="n">
@@ -17854,6 +18646,7 @@
       <c r="F787" t="n">
         <v>8</v>
       </c>
+      <c r="G787" t="inlineStr"/>
     </row>
     <row r="788">
       <c r="A788" t="n">
@@ -17876,6 +18669,7 @@
       <c r="F788" t="n">
         <v>8</v>
       </c>
+      <c r="G788" t="inlineStr"/>
     </row>
     <row r="789">
       <c r="A789" t="n">
@@ -17898,6 +18692,7 @@
       <c r="F789" t="n">
         <v>8</v>
       </c>
+      <c r="G789" t="inlineStr"/>
     </row>
     <row r="790">
       <c r="A790" t="n">
@@ -17920,6 +18715,7 @@
       <c r="F790" t="n">
         <v>8</v>
       </c>
+      <c r="G790" t="inlineStr"/>
     </row>
     <row r="791">
       <c r="A791" t="n">
@@ -17942,6 +18738,7 @@
       <c r="F791" t="n">
         <v>8</v>
       </c>
+      <c r="G791" t="inlineStr"/>
     </row>
     <row r="792">
       <c r="A792" t="n">
@@ -17964,6 +18761,7 @@
       <c r="F792" t="n">
         <v>8</v>
       </c>
+      <c r="G792" t="inlineStr"/>
     </row>
     <row r="793">
       <c r="A793" t="n">
@@ -17986,6 +18784,7 @@
       <c r="F793" t="n">
         <v>8</v>
       </c>
+      <c r="G793" t="inlineStr"/>
     </row>
     <row r="794">
       <c r="A794" t="n">
@@ -18008,6 +18807,7 @@
       <c r="F794" t="n">
         <v>8</v>
       </c>
+      <c r="G794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="n">
@@ -18030,6 +18830,7 @@
       <c r="F795" t="n">
         <v>8</v>
       </c>
+      <c r="G795" t="inlineStr"/>
     </row>
     <row r="796">
       <c r="A796" t="n">
@@ -18052,6 +18853,7 @@
       <c r="F796" t="n">
         <v>8</v>
       </c>
+      <c r="G796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="n">
@@ -18074,6 +18876,7 @@
       <c r="F797" t="n">
         <v>8</v>
       </c>
+      <c r="G797" t="inlineStr"/>
     </row>
     <row r="798">
       <c r="A798" t="n">
@@ -18096,6 +18899,7 @@
       <c r="F798" t="n">
         <v>8</v>
       </c>
+      <c r="G798" t="inlineStr"/>
     </row>
     <row r="799">
       <c r="A799" t="n">
@@ -18118,6 +18922,7 @@
       <c r="F799" t="n">
         <v>8</v>
       </c>
+      <c r="G799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -18140,6 +18945,7 @@
       <c r="F800" t="n">
         <v>8</v>
       </c>
+      <c r="G800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -18162,6 +18968,7 @@
       <c r="F801" t="n">
         <v>8</v>
       </c>
+      <c r="G801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="n">
@@ -18184,6 +18991,7 @@
       <c r="F802" t="n">
         <v>8</v>
       </c>
+      <c r="G802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -18206,6 +19014,7 @@
       <c r="F803" t="n">
         <v>8</v>
       </c>
+      <c r="G803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="n">
@@ -18228,6 +19037,7 @@
       <c r="F804" t="n">
         <v>8</v>
       </c>
+      <c r="G804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -18250,6 +19060,7 @@
       <c r="F805" t="n">
         <v>8</v>
       </c>
+      <c r="G805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="n">
@@ -18272,6 +19083,7 @@
       <c r="F806" t="n">
         <v>8</v>
       </c>
+      <c r="G806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="n">
@@ -18294,6 +19106,7 @@
       <c r="F807" t="n">
         <v>8</v>
       </c>
+      <c r="G807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="n">
@@ -18316,6 +19129,7 @@
       <c r="F808" t="n">
         <v>8</v>
       </c>
+      <c r="G808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="n">
@@ -18338,6 +19152,7 @@
       <c r="F809" t="n">
         <v>8</v>
       </c>
+      <c r="G809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="n">
@@ -18360,6 +19175,7 @@
       <c r="F810" t="n">
         <v>8</v>
       </c>
+      <c r="G810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="n">
@@ -18382,6 +19198,7 @@
       <c r="F811" t="n">
         <v>8</v>
       </c>
+      <c r="G811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="n">
@@ -18404,6 +19221,7 @@
       <c r="F812" t="n">
         <v>8</v>
       </c>
+      <c r="G812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="n">
@@ -18426,6 +19244,7 @@
       <c r="F813" t="n">
         <v>8</v>
       </c>
+      <c r="G813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="n">
@@ -18448,6 +19267,7 @@
       <c r="F814" t="n">
         <v>8</v>
       </c>
+      <c r="G814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="n">
@@ -18470,6 +19290,7 @@
       <c r="F815" t="n">
         <v>8</v>
       </c>
+      <c r="G815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="n">
@@ -18492,6 +19313,7 @@
       <c r="F816" t="n">
         <v>8</v>
       </c>
+      <c r="G816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -18514,6 +19336,7 @@
       <c r="F817" t="n">
         <v>8</v>
       </c>
+      <c r="G817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -18536,6 +19359,7 @@
       <c r="F818" t="n">
         <v>8</v>
       </c>
+      <c r="G818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="n">
@@ -18558,6 +19382,7 @@
       <c r="F819" t="n">
         <v>8</v>
       </c>
+      <c r="G819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -18580,6 +19405,7 @@
       <c r="F820" t="n">
         <v>8</v>
       </c>
+      <c r="G820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="n">
@@ -18602,6 +19428,7 @@
       <c r="F821" t="n">
         <v>8</v>
       </c>
+      <c r="G821" t="inlineStr"/>
     </row>
     <row r="822">
       <c r="A822" t="n">
@@ -18624,6 +19451,7 @@
       <c r="F822" t="n">
         <v>8</v>
       </c>
+      <c r="G822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="n">
@@ -18646,6 +19474,7 @@
       <c r="F823" t="n">
         <v>8</v>
       </c>
+      <c r="G823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="n">
@@ -18668,6 +19497,7 @@
       <c r="F824" t="n">
         <v>8</v>
       </c>
+      <c r="G824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="n">
@@ -18690,6 +19520,7 @@
       <c r="F825" t="n">
         <v>8</v>
       </c>
+      <c r="G825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" t="n">
@@ -18712,6 +19543,7 @@
       <c r="F826" t="n">
         <v>8</v>
       </c>
+      <c r="G826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" t="n">
@@ -18734,6 +19566,7 @@
       <c r="F827" t="n">
         <v>8</v>
       </c>
+      <c r="G827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" t="n">
@@ -18756,6 +19589,7 @@
       <c r="F828" t="n">
         <v>8</v>
       </c>
+      <c r="G828" t="inlineStr"/>
     </row>
     <row r="829">
       <c r="A829" t="n">
@@ -18778,6 +19612,7 @@
       <c r="F829" t="n">
         <v>8</v>
       </c>
+      <c r="G829" t="inlineStr"/>
     </row>
     <row r="830">
       <c r="A830" t="n">
@@ -18800,6 +19635,7 @@
       <c r="F830" t="n">
         <v>8</v>
       </c>
+      <c r="G830" t="inlineStr"/>
     </row>
     <row r="831">
       <c r="A831" t="n">
@@ -18822,6 +19658,7 @@
       <c r="F831" t="n">
         <v>8</v>
       </c>
+      <c r="G831" t="inlineStr"/>
     </row>
     <row r="832">
       <c r="A832" t="n">
@@ -18844,6 +19681,7 @@
       <c r="F832" t="n">
         <v>8</v>
       </c>
+      <c r="G832" t="inlineStr"/>
     </row>
     <row r="833">
       <c r="A833" t="n">
@@ -18866,6 +19704,7 @@
       <c r="F833" t="n">
         <v>8</v>
       </c>
+      <c r="G833" t="inlineStr"/>
     </row>
     <row r="834">
       <c r="A834" t="n">
@@ -18888,6 +19727,7 @@
       <c r="F834" t="n">
         <v>8</v>
       </c>
+      <c r="G834" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" t="n">
@@ -18910,6 +19750,7 @@
       <c r="F835" t="n">
         <v>8</v>
       </c>
+      <c r="G835" t="inlineStr"/>
     </row>
     <row r="836">
       <c r="A836" t="n">
@@ -18932,6 +19773,7 @@
       <c r="F836" t="n">
         <v>8</v>
       </c>
+      <c r="G836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="n">
@@ -18954,6 +19796,7 @@
       <c r="F837" t="n">
         <v>8</v>
       </c>
+      <c r="G837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" t="n">
@@ -18976,6 +19819,7 @@
       <c r="F838" t="n">
         <v>8</v>
       </c>
+      <c r="G838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="n">
@@ -18998,6 +19842,7 @@
       <c r="F839" t="n">
         <v>8</v>
       </c>
+      <c r="G839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="n">
@@ -19020,6 +19865,7 @@
       <c r="F840" t="n">
         <v>8</v>
       </c>
+      <c r="G840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" t="n">
@@ -19042,6 +19888,7 @@
       <c r="F841" t="n">
         <v>8</v>
       </c>
+      <c r="G841" t="inlineStr"/>
     </row>
     <row r="842">
       <c r="A842" t="n">
@@ -19064,6 +19911,7 @@
       <c r="F842" t="n">
         <v>8</v>
       </c>
+      <c r="G842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="n">
@@ -19086,6 +19934,7 @@
       <c r="F843" t="n">
         <v>8</v>
       </c>
+      <c r="G843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="n">
@@ -19108,6 +19957,7 @@
       <c r="F844" t="n">
         <v>8</v>
       </c>
+      <c r="G844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="n">
@@ -19130,6 +19980,7 @@
       <c r="F845" t="n">
         <v>8</v>
       </c>
+      <c r="G845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="n">
@@ -19152,6 +20003,7 @@
       <c r="F846" t="n">
         <v>8</v>
       </c>
+      <c r="G846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="n">
@@ -19174,6 +20026,7 @@
       <c r="F847" t="n">
         <v>8</v>
       </c>
+      <c r="G847" t="inlineStr"/>
     </row>
     <row r="848">
       <c r="A848" t="n">
@@ -19196,6 +20049,7 @@
       <c r="F848" t="n">
         <v>8</v>
       </c>
+      <c r="G848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="n">
@@ -19218,6 +20072,7 @@
       <c r="F849" t="n">
         <v>8</v>
       </c>
+      <c r="G849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="n">
@@ -19240,6 +20095,7 @@
       <c r="F850" t="n">
         <v>8</v>
       </c>
+      <c r="G850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="n">
@@ -19262,6 +20118,7 @@
       <c r="F851" t="n">
         <v>8</v>
       </c>
+      <c r="G851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="n">
@@ -19284,6 +20141,7 @@
       <c r="F852" t="n">
         <v>8</v>
       </c>
+      <c r="G852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" t="n">
@@ -19306,6 +20164,7 @@
       <c r="F853" t="n">
         <v>8</v>
       </c>
+      <c r="G853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="n">
@@ -19328,6 +20187,7 @@
       <c r="F854" t="n">
         <v>8</v>
       </c>
+      <c r="G854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="n">
@@ -19350,6 +20210,7 @@
       <c r="F855" t="n">
         <v>8</v>
       </c>
+      <c r="G855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="n">
@@ -19372,6 +20233,7 @@
       <c r="F856" t="n">
         <v>8</v>
       </c>
+      <c r="G856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="n">
@@ -19394,6 +20256,7 @@
       <c r="F857" t="n">
         <v>8</v>
       </c>
+      <c r="G857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="n">
@@ -19416,6 +20279,7 @@
       <c r="F858" t="n">
         <v>8</v>
       </c>
+      <c r="G858" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" t="n">
@@ -19438,6 +20302,7 @@
       <c r="F859" t="n">
         <v>8</v>
       </c>
+      <c r="G859" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" t="n">
@@ -19460,6 +20325,7 @@
       <c r="F860" t="n">
         <v>8</v>
       </c>
+      <c r="G860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" t="n">
@@ -19482,6 +20348,7 @@
       <c r="F861" t="n">
         <v>8</v>
       </c>
+      <c r="G861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" t="n">
@@ -19504,6 +20371,7 @@
       <c r="F862" t="n">
         <v>8</v>
       </c>
+      <c r="G862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="n">
@@ -19526,6 +20394,7 @@
       <c r="F863" t="n">
         <v>8</v>
       </c>
+      <c r="G863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" t="n">
@@ -19548,6 +20417,7 @@
       <c r="F864" t="n">
         <v>8</v>
       </c>
+      <c r="G864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" t="n">
@@ -19570,6 +20440,7 @@
       <c r="F865" t="n">
         <v>8</v>
       </c>
+      <c r="G865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" t="n">
@@ -19592,6 +20463,7 @@
       <c r="F866" t="n">
         <v>8</v>
       </c>
+      <c r="G866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="n">
@@ -19614,6 +20486,7 @@
       <c r="F867" t="n">
         <v>8</v>
       </c>
+      <c r="G867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="n">
@@ -19636,6 +20509,7 @@
       <c r="F868" t="n">
         <v>8</v>
       </c>
+      <c r="G868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="n">
@@ -19658,6 +20532,7 @@
       <c r="F869" t="n">
         <v>8</v>
       </c>
+      <c r="G869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" t="n">
@@ -19680,6 +20555,7 @@
       <c r="F870" t="n">
         <v>8</v>
       </c>
+      <c r="G870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" t="n">
@@ -19702,6 +20578,7 @@
       <c r="F871" t="n">
         <v>8</v>
       </c>
+      <c r="G871" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" t="n">
@@ -19724,6 +20601,7 @@
       <c r="F872" t="n">
         <v>8</v>
       </c>
+      <c r="G872" t="inlineStr"/>
     </row>
     <row r="873">
       <c r="A873" t="n">
@@ -19746,6 +20624,7 @@
       <c r="F873" t="n">
         <v>8</v>
       </c>
+      <c r="G873" t="inlineStr"/>
     </row>
     <row r="874">
       <c r="A874" t="n">
@@ -19768,6 +20647,7 @@
       <c r="F874" t="n">
         <v>8</v>
       </c>
+      <c r="G874" t="inlineStr"/>
     </row>
     <row r="875">
       <c r="A875" t="n">
@@ -19790,6 +20670,7 @@
       <c r="F875" t="n">
         <v>8</v>
       </c>
+      <c r="G875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" t="n">
@@ -19812,6 +20693,7 @@
       <c r="F876" t="n">
         <v>8</v>
       </c>
+      <c r="G876" t="inlineStr"/>
     </row>
     <row r="877">
       <c r="A877" t="n">
@@ -19834,6 +20716,7 @@
       <c r="F877" t="n">
         <v>8</v>
       </c>
+      <c r="G877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="n">
@@ -19856,6 +20739,7 @@
       <c r="F878" t="n">
         <v>8</v>
       </c>
+      <c r="G878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" t="n">
@@ -19878,6 +20762,7 @@
       <c r="F879" t="n">
         <v>8</v>
       </c>
+      <c r="G879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="n">
@@ -19900,6 +20785,7 @@
       <c r="F880" t="n">
         <v>8</v>
       </c>
+      <c r="G880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" t="n">
@@ -19922,6 +20808,7 @@
       <c r="F881" t="n">
         <v>8</v>
       </c>
+      <c r="G881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="n">
@@ -19944,6 +20831,7 @@
       <c r="F882" t="n">
         <v>8</v>
       </c>
+      <c r="G882" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" t="n">
@@ -19966,6 +20854,7 @@
       <c r="F883" t="n">
         <v>8</v>
       </c>
+      <c r="G883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="n">
@@ -19988,6 +20877,7 @@
       <c r="F884" t="n">
         <v>8</v>
       </c>
+      <c r="G884" t="inlineStr"/>
     </row>
     <row r="885">
       <c r="A885" t="n">
@@ -20010,6 +20900,7 @@
       <c r="F885" t="n">
         <v>8</v>
       </c>
+      <c r="G885" t="inlineStr"/>
     </row>
     <row r="886">
       <c r="A886" t="n">
@@ -20032,6 +20923,7 @@
       <c r="F886" t="n">
         <v>8</v>
       </c>
+      <c r="G886" t="inlineStr"/>
     </row>
     <row r="887">
       <c r="A887" t="n">
@@ -20054,6 +20946,7 @@
       <c r="F887" t="n">
         <v>8</v>
       </c>
+      <c r="G887" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" t="n">
@@ -20076,6 +20969,7 @@
       <c r="F888" t="n">
         <v>8</v>
       </c>
+      <c r="G888" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" t="n">
@@ -20098,6 +20992,7 @@
       <c r="F889" t="n">
         <v>8</v>
       </c>
+      <c r="G889" t="inlineStr"/>
     </row>
     <row r="890">
       <c r="A890" t="n">
@@ -20120,6 +21015,7 @@
       <c r="F890" t="n">
         <v>8</v>
       </c>
+      <c r="G890" t="inlineStr"/>
     </row>
     <row r="891">
       <c r="A891" t="n">
@@ -20142,6 +21038,7 @@
       <c r="F891" t="n">
         <v>8</v>
       </c>
+      <c r="G891" t="inlineStr"/>
     </row>
     <row r="892">
       <c r="A892" t="n">
@@ -20164,6 +21061,7 @@
       <c r="F892" t="n">
         <v>8</v>
       </c>
+      <c r="G892" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" t="n">
@@ -20186,6 +21084,7 @@
       <c r="F893" t="n">
         <v>8</v>
       </c>
+      <c r="G893" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" t="n">
@@ -20208,6 +21107,7 @@
       <c r="F894" t="n">
         <v>8</v>
       </c>
+      <c r="G894" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" t="n">
@@ -20230,6 +21130,7 @@
       <c r="F895" t="n">
         <v>8</v>
       </c>
+      <c r="G895" t="inlineStr"/>
     </row>
     <row r="896">
       <c r="A896" t="n">
@@ -20252,6 +21153,7 @@
       <c r="F896" t="n">
         <v>8</v>
       </c>
+      <c r="G896" t="inlineStr"/>
     </row>
     <row r="897">
       <c r="A897" t="n">
@@ -20274,6 +21176,7 @@
       <c r="F897" t="n">
         <v>8</v>
       </c>
+      <c r="G897" t="inlineStr"/>
     </row>
     <row r="898">
       <c r="A898" t="n">
@@ -20296,6 +21199,7 @@
       <c r="F898" t="n">
         <v>8</v>
       </c>
+      <c r="G898" t="inlineStr"/>
     </row>
     <row r="899">
       <c r="A899" t="n">
@@ -20318,6 +21222,7 @@
       <c r="F899" t="n">
         <v>8</v>
       </c>
+      <c r="G899" t="inlineStr"/>
     </row>
     <row r="900">
       <c r="A900" t="n">
@@ -20340,6 +21245,7 @@
       <c r="F900" t="n">
         <v>8</v>
       </c>
+      <c r="G900" t="inlineStr"/>
     </row>
     <row r="901">
       <c r="A901" t="n">
@@ -20362,6 +21268,7 @@
       <c r="F901" t="n">
         <v>8</v>
       </c>
+      <c r="G901" t="inlineStr"/>
     </row>
     <row r="902">
       <c r="A902" t="n">
@@ -20384,6 +21291,7 @@
       <c r="F902" t="n">
         <v>8</v>
       </c>
+      <c r="G902" t="inlineStr"/>
     </row>
     <row r="903">
       <c r="A903" t="n">
@@ -20406,6 +21314,7 @@
       <c r="F903" t="n">
         <v>8</v>
       </c>
+      <c r="G903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" t="n">
@@ -20428,6 +21337,7 @@
       <c r="F904" t="n">
         <v>8</v>
       </c>
+      <c r="G904" t="inlineStr"/>
     </row>
     <row r="905">
       <c r="A905" t="n">
@@ -20450,6 +21360,7 @@
       <c r="F905" t="n">
         <v>8</v>
       </c>
+      <c r="G905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" t="n">
@@ -20472,6 +21383,7 @@
       <c r="F906" t="n">
         <v>8</v>
       </c>
+      <c r="G906" t="inlineStr"/>
     </row>
     <row r="907">
       <c r="A907" t="n">
@@ -20494,6 +21406,7 @@
       <c r="F907" t="n">
         <v>8</v>
       </c>
+      <c r="G907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" t="n">
@@ -20516,6 +21429,7 @@
       <c r="F908" t="n">
         <v>8</v>
       </c>
+      <c r="G908" t="inlineStr"/>
     </row>
     <row r="909">
       <c r="A909" t="n">
@@ -20538,6 +21452,7 @@
       <c r="F909" t="n">
         <v>8</v>
       </c>
+      <c r="G909" t="inlineStr"/>
     </row>
     <row r="910">
       <c r="A910" t="n">
@@ -20560,6 +21475,7 @@
       <c r="F910" t="n">
         <v>8</v>
       </c>
+      <c r="G910" t="inlineStr"/>
     </row>
     <row r="911">
       <c r="A911" t="n">
@@ -20582,6 +21498,7 @@
       <c r="F911" t="n">
         <v>8</v>
       </c>
+      <c r="G911" t="inlineStr"/>
     </row>
     <row r="912">
       <c r="A912" t="n">
@@ -20604,6 +21521,7 @@
       <c r="F912" t="n">
         <v>8</v>
       </c>
+      <c r="G912" t="inlineStr"/>
     </row>
     <row r="913">
       <c r="A913" t="n">
@@ -20626,6 +21544,7 @@
       <c r="F913" t="n">
         <v>8</v>
       </c>
+      <c r="G913" t="inlineStr"/>
     </row>
     <row r="914">
       <c r="A914" t="n">
@@ -20648,6 +21567,7 @@
       <c r="F914" t="n">
         <v>8</v>
       </c>
+      <c r="G914" t="inlineStr"/>
     </row>
     <row r="915">
       <c r="A915" t="n">
@@ -20670,6 +21590,7 @@
       <c r="F915" t="n">
         <v>8</v>
       </c>
+      <c r="G915" t="inlineStr"/>
     </row>
     <row r="916">
       <c r="A916" t="n">
@@ -20692,6 +21613,7 @@
       <c r="F916" t="n">
         <v>8</v>
       </c>
+      <c r="G916" t="inlineStr"/>
     </row>
     <row r="917">
       <c r="A917" t="n">
@@ -20714,6 +21636,7 @@
       <c r="F917" t="n">
         <v>8</v>
       </c>
+      <c r="G917" t="inlineStr"/>
     </row>
     <row r="918">
       <c r="A918" t="n">
@@ -20736,6 +21659,7 @@
       <c r="F918" t="n">
         <v>8</v>
       </c>
+      <c r="G918" t="inlineStr"/>
     </row>
     <row r="919">
       <c r="A919" t="n">
@@ -20758,6 +21682,7 @@
       <c r="F919" t="n">
         <v>8</v>
       </c>
+      <c r="G919" t="inlineStr"/>
     </row>
     <row r="920">
       <c r="A920" t="n">
@@ -20780,6 +21705,7 @@
       <c r="F920" t="n">
         <v>8</v>
       </c>
+      <c r="G920" t="inlineStr"/>
     </row>
     <row r="921">
       <c r="A921" t="n">
@@ -20802,6 +21728,7 @@
       <c r="F921" t="n">
         <v>8</v>
       </c>
+      <c r="G921" t="inlineStr"/>
     </row>
     <row r="922">
       <c r="A922" t="n">
@@ -20824,6 +21751,7 @@
       <c r="F922" t="n">
         <v>8</v>
       </c>
+      <c r="G922" t="inlineStr"/>
     </row>
     <row r="923">
       <c r="A923" t="n">
@@ -20846,6 +21774,7 @@
       <c r="F923" t="n">
         <v>8</v>
       </c>
+      <c r="G923" t="inlineStr"/>
     </row>
     <row r="924">
       <c r="A924" t="n">
@@ -20868,6 +21797,7 @@
       <c r="F924" t="n">
         <v>8</v>
       </c>
+      <c r="G924" t="inlineStr"/>
     </row>
     <row r="925">
       <c r="A925" t="n">
@@ -20890,6 +21820,7 @@
       <c r="F925" t="n">
         <v>8</v>
       </c>
+      <c r="G925" t="inlineStr"/>
     </row>
     <row r="926">
       <c r="A926" t="n">
@@ -20912,6 +21843,7 @@
       <c r="F926" t="n">
         <v>8</v>
       </c>
+      <c r="G926" t="inlineStr"/>
     </row>
     <row r="927">
       <c r="A927" t="n">
@@ -20934,6 +21866,7 @@
       <c r="F927" t="n">
         <v>8</v>
       </c>
+      <c r="G927" t="inlineStr"/>
     </row>
     <row r="928">
       <c r="A928" t="n">
@@ -20956,6 +21889,7 @@
       <c r="F928" t="n">
         <v>8</v>
       </c>
+      <c r="G928" t="inlineStr"/>
     </row>
     <row r="929">
       <c r="A929" t="n">
@@ -20978,6 +21912,7 @@
       <c r="F929" t="n">
         <v>8</v>
       </c>
+      <c r="G929" t="inlineStr"/>
     </row>
     <row r="930">
       <c r="A930" t="n">
@@ -21000,6 +21935,7 @@
       <c r="F930" t="n">
         <v>8</v>
       </c>
+      <c r="G930" t="inlineStr"/>
     </row>
     <row r="931">
       <c r="A931" t="n">
@@ -21022,6 +21958,7 @@
       <c r="F931" t="n">
         <v>8</v>
       </c>
+      <c r="G931" t="inlineStr"/>
     </row>
     <row r="932">
       <c r="A932" t="n">
@@ -21044,6 +21981,7 @@
       <c r="F932" t="n">
         <v>8</v>
       </c>
+      <c r="G932" t="inlineStr"/>
     </row>
     <row r="933">
       <c r="A933" t="n">
@@ -21066,6 +22004,7 @@
       <c r="F933" t="n">
         <v>8</v>
       </c>
+      <c r="G933" t="inlineStr"/>
     </row>
     <row r="934">
       <c r="A934" t="n">
@@ -21088,6 +22027,7 @@
       <c r="F934" t="n">
         <v>8</v>
       </c>
+      <c r="G934" t="inlineStr"/>
     </row>
     <row r="935">
       <c r="A935" t="n">
@@ -21110,6 +22050,7 @@
       <c r="F935" t="n">
         <v>8</v>
       </c>
+      <c r="G935" t="inlineStr"/>
     </row>
     <row r="936">
       <c r="A936" t="n">
@@ -21132,6 +22073,7 @@
       <c r="F936" t="n">
         <v>8</v>
       </c>
+      <c r="G936" t="inlineStr"/>
     </row>
     <row r="937">
       <c r="A937" t="n">
@@ -21154,6 +22096,7 @@
       <c r="F937" t="n">
         <v>8</v>
       </c>
+      <c r="G937" t="inlineStr"/>
     </row>
     <row r="938">
       <c r="A938" t="n">
@@ -21176,6 +22119,7 @@
       <c r="F938" t="n">
         <v>8</v>
       </c>
+      <c r="G938" t="inlineStr"/>
     </row>
     <row r="939">
       <c r="A939" t="n">
@@ -21198,6 +22142,7 @@
       <c r="F939" t="n">
         <v>8</v>
       </c>
+      <c r="G939" t="inlineStr"/>
     </row>
     <row r="940">
       <c r="A940" t="n">
@@ -21220,6 +22165,7 @@
       <c r="F940" t="n">
         <v>8</v>
       </c>
+      <c r="G940" t="inlineStr"/>
     </row>
     <row r="941">
       <c r="A941" t="n">
@@ -21242,6 +22188,7 @@
       <c r="F941" t="n">
         <v>8</v>
       </c>
+      <c r="G941" t="inlineStr"/>
     </row>
     <row r="942">
       <c r="A942" t="n">
@@ -21264,6 +22211,7 @@
       <c r="F942" t="n">
         <v>8</v>
       </c>
+      <c r="G942" t="inlineStr"/>
     </row>
     <row r="943">
       <c r="A943" t="n">
@@ -21286,6 +22234,7 @@
       <c r="F943" t="n">
         <v>8</v>
       </c>
+      <c r="G943" t="inlineStr"/>
     </row>
     <row r="944">
       <c r="A944" t="n">
@@ -21308,6 +22257,7 @@
       <c r="F944" t="n">
         <v>8</v>
       </c>
+      <c r="G944" t="inlineStr"/>
     </row>
     <row r="945">
       <c r="A945" t="n">
@@ -21330,6 +22280,7 @@
       <c r="F945" t="n">
         <v>8</v>
       </c>
+      <c r="G945" t="inlineStr"/>
     </row>
     <row r="946">
       <c r="A946" t="n">
@@ -21352,6 +22303,7 @@
       <c r="F946" t="n">
         <v>8</v>
       </c>
+      <c r="G946" t="inlineStr"/>
     </row>
     <row r="947">
       <c r="A947" t="n">
@@ -21374,6 +22326,7 @@
       <c r="F947" t="n">
         <v>8</v>
       </c>
+      <c r="G947" t="inlineStr"/>
     </row>
     <row r="948">
       <c r="A948" t="n">
@@ -21396,6 +22349,7 @@
       <c r="F948" t="n">
         <v>8</v>
       </c>
+      <c r="G948" t="inlineStr"/>
     </row>
     <row r="949">
       <c r="A949" t="n">
@@ -21418,6 +22372,7 @@
       <c r="F949" t="n">
         <v>8</v>
       </c>
+      <c r="G949" t="inlineStr"/>
     </row>
     <row r="950">
       <c r="A950" t="n">
@@ -21440,6 +22395,7 @@
       <c r="F950" t="n">
         <v>8</v>
       </c>
+      <c r="G950" t="inlineStr"/>
     </row>
     <row r="951">
       <c r="A951" t="n">
@@ -21462,6 +22418,7 @@
       <c r="F951" t="n">
         <v>8</v>
       </c>
+      <c r="G951" t="inlineStr"/>
     </row>
     <row r="952">
       <c r="A952" t="n">
@@ -21484,6 +22441,7 @@
       <c r="F952" t="n">
         <v>8</v>
       </c>
+      <c r="G952" t="inlineStr"/>
     </row>
     <row r="953">
       <c r="A953" t="n">
@@ -21506,6 +22464,7 @@
       <c r="F953" t="n">
         <v>8</v>
       </c>
+      <c r="G953" t="inlineStr"/>
     </row>
     <row r="954">
       <c r="A954" t="n">
@@ -21528,6 +22487,7 @@
       <c r="F954" t="n">
         <v>8</v>
       </c>
+      <c r="G954" t="inlineStr"/>
     </row>
     <row r="955">
       <c r="A955" t="n">
@@ -21550,6 +22510,7 @@
       <c r="F955" t="n">
         <v>8</v>
       </c>
+      <c r="G955" t="inlineStr"/>
     </row>
     <row r="956">
       <c r="A956" t="n">
@@ -21572,6 +22533,7 @@
       <c r="F956" t="n">
         <v>8</v>
       </c>
+      <c r="G956" t="inlineStr"/>
     </row>
     <row r="957">
       <c r="A957" t="n">
@@ -21594,6 +22556,7 @@
       <c r="F957" t="n">
         <v>8</v>
       </c>
+      <c r="G957" t="inlineStr"/>
     </row>
     <row r="958">
       <c r="A958" t="n">
@@ -21616,6 +22579,7 @@
       <c r="F958" t="n">
         <v>8</v>
       </c>
+      <c r="G958" t="inlineStr"/>
     </row>
     <row r="959">
       <c r="A959" t="n">
@@ -21638,6 +22602,7 @@
       <c r="F959" t="n">
         <v>8</v>
       </c>
+      <c r="G959" t="inlineStr"/>
     </row>
     <row r="960">
       <c r="A960" t="n">
@@ -21660,6 +22625,7 @@
       <c r="F960" t="n">
         <v>8</v>
       </c>
+      <c r="G960" t="inlineStr"/>
     </row>
     <row r="961">
       <c r="A961" t="n">
@@ -21682,6 +22648,7 @@
       <c r="F961" t="n">
         <v>8</v>
       </c>
+      <c r="G961" t="inlineStr"/>
     </row>
     <row r="962">
       <c r="A962" t="n">
@@ -21704,6 +22671,7 @@
       <c r="F962" t="n">
         <v>8</v>
       </c>
+      <c r="G962" t="inlineStr"/>
     </row>
     <row r="963">
       <c r="A963" t="n">
@@ -21726,6 +22694,7 @@
       <c r="F963" t="n">
         <v>8</v>
       </c>
+      <c r="G963" t="inlineStr"/>
     </row>
     <row r="964">
       <c r="A964" t="n">
@@ -21748,6 +22717,7 @@
       <c r="F964" t="n">
         <v>8</v>
       </c>
+      <c r="G964" t="inlineStr"/>
     </row>
     <row r="965">
       <c r="A965" t="n">
@@ -21770,6 +22740,7 @@
       <c r="F965" t="n">
         <v>8</v>
       </c>
+      <c r="G965" t="inlineStr"/>
     </row>
     <row r="966">
       <c r="A966" t="n">
@@ -21792,6 +22763,7 @@
       <c r="F966" t="n">
         <v>8</v>
       </c>
+      <c r="G966" t="inlineStr"/>
     </row>
     <row r="967">
       <c r="A967" t="n">
@@ -21814,6 +22786,7 @@
       <c r="F967" t="n">
         <v>8</v>
       </c>
+      <c r="G967" t="inlineStr"/>
     </row>
     <row r="968">
       <c r="A968" t="n">
@@ -21836,6 +22809,7 @@
       <c r="F968" t="n">
         <v>8</v>
       </c>
+      <c r="G968" t="inlineStr"/>
     </row>
     <row r="969">
       <c r="A969" t="n">
@@ -21858,6 +22832,7 @@
       <c r="F969" t="n">
         <v>8</v>
       </c>
+      <c r="G969" t="inlineStr"/>
     </row>
     <row r="970">
       <c r="A970" t="n">
@@ -21880,6 +22855,7 @@
       <c r="F970" t="n">
         <v>8</v>
       </c>
+      <c r="G970" t="inlineStr"/>
     </row>
     <row r="971">
       <c r="A971" t="n">
@@ -21902,6 +22878,7 @@
       <c r="F971" t="n">
         <v>8</v>
       </c>
+      <c r="G971" t="inlineStr"/>
     </row>
     <row r="972">
       <c r="A972" t="n">
@@ -21924,6 +22901,7 @@
       <c r="F972" t="n">
         <v>8</v>
       </c>
+      <c r="G972" t="inlineStr"/>
     </row>
     <row r="973">
       <c r="A973" t="n">
@@ -21946,6 +22924,7 @@
       <c r="F973" t="n">
         <v>8</v>
       </c>
+      <c r="G973" t="inlineStr"/>
     </row>
     <row r="974">
       <c r="A974" t="n">
@@ -21968,6 +22947,7 @@
       <c r="F974" t="n">
         <v>8</v>
       </c>
+      <c r="G974" t="inlineStr"/>
     </row>
     <row r="975">
       <c r="A975" t="n">
@@ -21990,6 +22970,7 @@
       <c r="F975" t="n">
         <v>8</v>
       </c>
+      <c r="G975" t="inlineStr"/>
     </row>
     <row r="976">
       <c r="A976" t="n">
@@ -22012,6 +22993,7 @@
       <c r="F976" t="n">
         <v>8</v>
       </c>
+      <c r="G976" t="inlineStr"/>
     </row>
     <row r="977">
       <c r="A977" t="n">
@@ -22034,6 +23016,7 @@
       <c r="F977" t="n">
         <v>8</v>
       </c>
+      <c r="G977" t="inlineStr"/>
     </row>
     <row r="978">
       <c r="A978" t="n">
@@ -22056,6 +23039,7 @@
       <c r="F978" t="n">
         <v>8</v>
       </c>
+      <c r="G978" t="inlineStr"/>
     </row>
     <row r="979">
       <c r="A979" t="n">
@@ -22078,6 +23062,7 @@
       <c r="F979" t="n">
         <v>8</v>
       </c>
+      <c r="G979" t="inlineStr"/>
     </row>
     <row r="980">
       <c r="A980" t="n">
@@ -22100,6 +23085,7 @@
       <c r="F980" t="n">
         <v>8</v>
       </c>
+      <c r="G980" t="inlineStr"/>
     </row>
     <row r="981">
       <c r="A981" t="n">
@@ -22122,6 +23108,7 @@
       <c r="F981" t="n">
         <v>8</v>
       </c>
+      <c r="G981" t="inlineStr"/>
     </row>
     <row r="982">
       <c r="A982" t="n">
@@ -22144,6 +23131,7 @@
       <c r="F982" t="n">
         <v>8</v>
       </c>
+      <c r="G982" t="inlineStr"/>
     </row>
     <row r="983">
       <c r="A983" t="n">
@@ -22166,6 +23154,7 @@
       <c r="F983" t="n">
         <v>8</v>
       </c>
+      <c r="G983" t="inlineStr"/>
     </row>
     <row r="984">
       <c r="A984" t="n">
@@ -22188,6 +23177,7 @@
       <c r="F984" t="n">
         <v>8</v>
       </c>
+      <c r="G984" t="inlineStr"/>
     </row>
     <row r="985">
       <c r="A985" t="n">
@@ -22210,6 +23200,7 @@
       <c r="F985" t="n">
         <v>8</v>
       </c>
+      <c r="G985" t="inlineStr"/>
     </row>
     <row r="986">
       <c r="A986" t="n">
@@ -22232,6 +23223,7 @@
       <c r="F986" t="n">
         <v>8</v>
       </c>
+      <c r="G986" t="inlineStr"/>
     </row>
     <row r="987">
       <c r="A987" t="n">
@@ -22254,6 +23246,7 @@
       <c r="F987" t="n">
         <v>8</v>
       </c>
+      <c r="G987" t="inlineStr"/>
     </row>
     <row r="988">
       <c r="A988" t="n">
@@ -22276,6 +23269,7 @@
       <c r="F988" t="n">
         <v>8</v>
       </c>
+      <c r="G988" t="inlineStr"/>
     </row>
     <row r="989">
       <c r="A989" t="n">
@@ -22298,6 +23292,7 @@
       <c r="F989" t="n">
         <v>8</v>
       </c>
+      <c r="G989" t="inlineStr"/>
     </row>
     <row r="990">
       <c r="A990" t="n">
@@ -22320,6 +23315,7 @@
       <c r="F990" t="n">
         <v>8</v>
       </c>
+      <c r="G990" t="inlineStr"/>
     </row>
     <row r="991">
       <c r="A991" t="n">
@@ -22342,6 +23338,7 @@
       <c r="F991" t="n">
         <v>8</v>
       </c>
+      <c r="G991" t="inlineStr"/>
     </row>
     <row r="992">
       <c r="A992" t="n">
@@ -22364,6 +23361,7 @@
       <c r="F992" t="n">
         <v>8</v>
       </c>
+      <c r="G992" t="inlineStr"/>
     </row>
     <row r="993">
       <c r="A993" t="n">
@@ -22386,6 +23384,7 @@
       <c r="F993" t="n">
         <v>8</v>
       </c>
+      <c r="G993" t="inlineStr"/>
     </row>
     <row r="994">
       <c r="A994" t="n">
@@ -22408,6 +23407,7 @@
       <c r="F994" t="n">
         <v>8</v>
       </c>
+      <c r="G994" t="inlineStr"/>
     </row>
     <row r="995">
       <c r="A995" t="n">
@@ -22430,6 +23430,7 @@
       <c r="F995" t="n">
         <v>8</v>
       </c>
+      <c r="G995" t="inlineStr"/>
     </row>
     <row r="996">
       <c r="A996" t="n">
@@ -22452,6 +23453,7 @@
       <c r="F996" t="n">
         <v>8</v>
       </c>
+      <c r="G996" t="inlineStr"/>
     </row>
     <row r="997">
       <c r="A997" t="n">
@@ -22474,6 +23476,7 @@
       <c r="F997" t="n">
         <v>8</v>
       </c>
+      <c r="G997" t="inlineStr"/>
     </row>
     <row r="998">
       <c r="A998" t="n">
@@ -22496,6 +23499,7 @@
       <c r="F998" t="n">
         <v>8</v>
       </c>
+      <c r="G998" t="inlineStr"/>
     </row>
     <row r="999">
       <c r="A999" t="n">
@@ -22518,6 +23522,7 @@
       <c r="F999" t="n">
         <v>8</v>
       </c>
+      <c r="G999" t="inlineStr"/>
     </row>
     <row r="1000">
       <c r="A1000" t="n">
@@ -22540,6 +23545,7 @@
       <c r="F1000" t="n">
         <v>8</v>
       </c>
+      <c r="G1000" t="inlineStr"/>
     </row>
     <row r="1001">
       <c r="A1001" t="n">
@@ -22562,6 +23568,7 @@
       <c r="F1001" t="n">
         <v>8</v>
       </c>
+      <c r="G1001" t="inlineStr"/>
     </row>
     <row r="1002">
       <c r="A1002" t="n">
@@ -22584,6 +23591,7 @@
       <c r="F1002" t="n">
         <v>8</v>
       </c>
+      <c r="G1002" t="inlineStr"/>
     </row>
     <row r="1003">
       <c r="A1003" t="n">
@@ -22606,6 +23614,7 @@
       <c r="F1003" t="n">
         <v>8</v>
       </c>
+      <c r="G1003" t="inlineStr"/>
     </row>
     <row r="1004">
       <c r="A1004" t="n">
@@ -22628,6 +23637,7 @@
       <c r="F1004" t="n">
         <v>8</v>
       </c>
+      <c r="G1004" t="inlineStr"/>
     </row>
     <row r="1005">
       <c r="A1005" t="n">
@@ -22650,6 +23660,7 @@
       <c r="F1005" t="n">
         <v>8</v>
       </c>
+      <c r="G1005" t="inlineStr"/>
     </row>
     <row r="1006">
       <c r="A1006" t="n">
@@ -22672,6 +23683,7 @@
       <c r="F1006" t="n">
         <v>8</v>
       </c>
+      <c r="G1006" t="inlineStr"/>
     </row>
     <row r="1007">
       <c r="A1007" t="n">
@@ -22694,6 +23706,7 @@
       <c r="F1007" t="n">
         <v>8</v>
       </c>
+      <c r="G1007" t="inlineStr"/>
     </row>
     <row r="1008">
       <c r="A1008" t="n">
@@ -22716,6 +23729,7 @@
       <c r="F1008" t="n">
         <v>8</v>
       </c>
+      <c r="G1008" t="inlineStr"/>
     </row>
     <row r="1009">
       <c r="A1009" t="n">
@@ -22738,6 +23752,7 @@
       <c r="F1009" t="n">
         <v>8</v>
       </c>
+      <c r="G1009" t="inlineStr"/>
     </row>
     <row r="1010">
       <c r="A1010" t="n">
@@ -22760,6 +23775,7 @@
       <c r="F1010" t="n">
         <v>8</v>
       </c>
+      <c r="G1010" t="inlineStr"/>
     </row>
     <row r="1011">
       <c r="A1011" t="n">
@@ -22782,6 +23798,7 @@
       <c r="F1011" t="n">
         <v>8</v>
       </c>
+      <c r="G1011" t="inlineStr"/>
     </row>
     <row r="1012">
       <c r="A1012" t="n">
@@ -22804,6 +23821,7 @@
       <c r="F1012" t="n">
         <v>8</v>
       </c>
+      <c r="G1012" t="inlineStr"/>
     </row>
     <row r="1013">
       <c r="A1013" t="n">
@@ -22826,6 +23844,7 @@
       <c r="F1013" t="n">
         <v>8</v>
       </c>
+      <c r="G1013" t="inlineStr"/>
     </row>
     <row r="1014">
       <c r="A1014" t="n">
@@ -22848,6 +23867,7 @@
       <c r="F1014" t="n">
         <v>8</v>
       </c>
+      <c r="G1014" t="inlineStr"/>
     </row>
     <row r="1015">
       <c r="A1015" t="n">
@@ -22870,6 +23890,7 @@
       <c r="F1015" t="n">
         <v>8</v>
       </c>
+      <c r="G1015" t="inlineStr"/>
     </row>
     <row r="1016">
       <c r="A1016" t="n">
@@ -22892,6 +23913,7 @@
       <c r="F1016" t="n">
         <v>8</v>
       </c>
+      <c r="G1016" t="inlineStr"/>
     </row>
     <row r="1017">
       <c r="A1017" t="n">
@@ -22914,6 +23936,7 @@
       <c r="F1017" t="n">
         <v>8</v>
       </c>
+      <c r="G1017" t="inlineStr"/>
     </row>
     <row r="1018">
       <c r="A1018" t="n">
@@ -22936,6 +23959,7 @@
       <c r="F1018" t="n">
         <v>8</v>
       </c>
+      <c r="G1018" t="inlineStr"/>
     </row>
     <row r="1019">
       <c r="A1019" t="n">
@@ -22958,6 +23982,7 @@
       <c r="F1019" t="n">
         <v>8</v>
       </c>
+      <c r="G1019" t="inlineStr"/>
     </row>
     <row r="1020">
       <c r="A1020" t="n">
@@ -22980,6 +24005,7 @@
       <c r="F1020" t="n">
         <v>8</v>
       </c>
+      <c r="G1020" t="inlineStr"/>
     </row>
     <row r="1021">
       <c r="A1021" t="n">
@@ -23002,6 +24028,7 @@
       <c r="F1021" t="n">
         <v>8</v>
       </c>
+      <c r="G1021" t="inlineStr"/>
     </row>
     <row r="1022">
       <c r="A1022" t="n">
@@ -23024,6 +24051,7 @@
       <c r="F1022" t="n">
         <v>8</v>
       </c>
+      <c r="G1022" t="inlineStr"/>
     </row>
     <row r="1023">
       <c r="A1023" t="n">
@@ -23046,6 +24074,7 @@
       <c r="F1023" t="n">
         <v>8</v>
       </c>
+      <c r="G1023" t="inlineStr"/>
     </row>
     <row r="1024">
       <c r="A1024" t="n">
@@ -23068,6 +24097,7 @@
       <c r="F1024" t="n">
         <v>8</v>
       </c>
+      <c r="G1024" t="inlineStr"/>
     </row>
     <row r="1025">
       <c r="A1025" t="n">
@@ -23090,6 +24120,7 @@
       <c r="F1025" t="n">
         <v>8</v>
       </c>
+      <c r="G1025" t="inlineStr"/>
     </row>
     <row r="1026">
       <c r="A1026" t="n">
@@ -23112,6 +24143,7 @@
       <c r="F1026" t="n">
         <v>8</v>
       </c>
+      <c r="G1026" t="inlineStr"/>
     </row>
     <row r="1027">
       <c r="A1027" t="n">
@@ -23134,6 +24166,7 @@
       <c r="F1027" t="n">
         <v>8</v>
       </c>
+      <c r="G1027" t="inlineStr"/>
     </row>
     <row r="1028">
       <c r="A1028" t="n">
@@ -23156,6 +24189,7 @@
       <c r="F1028" t="n">
         <v>8</v>
       </c>
+      <c r="G1028" t="inlineStr"/>
     </row>
     <row r="1029">
       <c r="A1029" t="n">
@@ -23178,6 +24212,7 @@
       <c r="F1029" t="n">
         <v>8</v>
       </c>
+      <c r="G1029" t="inlineStr"/>
     </row>
     <row r="1030">
       <c r="A1030" t="n">
@@ -23200,6 +24235,7 @@
       <c r="F1030" t="n">
         <v>8</v>
       </c>
+      <c r="G1030" t="inlineStr"/>
     </row>
     <row r="1031">
       <c r="A1031" t="n">
@@ -23222,6 +24258,7 @@
       <c r="F1031" t="n">
         <v>8</v>
       </c>
+      <c r="G1031" t="inlineStr"/>
     </row>
     <row r="1032">
       <c r="A1032" t="n">
@@ -23244,6 +24281,7 @@
       <c r="F1032" t="n">
         <v>8</v>
       </c>
+      <c r="G1032" t="inlineStr"/>
     </row>
     <row r="1033">
       <c r="A1033" t="n">
@@ -23266,6 +24304,7 @@
       <c r="F1033" t="n">
         <v>8</v>
       </c>
+      <c r="G1033" t="inlineStr"/>
     </row>
     <row r="1034">
       <c r="A1034" t="n">
@@ -23288,6 +24327,7 @@
       <c r="F1034" t="n">
         <v>8</v>
       </c>
+      <c r="G1034" t="inlineStr"/>
     </row>
     <row r="1035">
       <c r="A1035" t="n">
@@ -23310,6 +24350,7 @@
       <c r="F1035" t="n">
         <v>8</v>
       </c>
+      <c r="G1035" t="inlineStr"/>
     </row>
     <row r="1036">
       <c r="A1036" t="n">
@@ -23332,6 +24373,7 @@
       <c r="F1036" t="n">
         <v>8</v>
       </c>
+      <c r="G1036" t="inlineStr"/>
     </row>
     <row r="1037">
       <c r="A1037" t="n">
@@ -23354,6 +24396,7 @@
       <c r="F1037" t="n">
         <v>8</v>
       </c>
+      <c r="G1037" t="inlineStr"/>
     </row>
     <row r="1038">
       <c r="A1038" t="n">
@@ -23376,6 +24419,7 @@
       <c r="F1038" t="n">
         <v>8</v>
       </c>
+      <c r="G1038" t="inlineStr"/>
     </row>
     <row r="1039">
       <c r="A1039" t="n">
@@ -23398,6 +24442,7 @@
       <c r="F1039" t="n">
         <v>8</v>
       </c>
+      <c r="G1039" t="inlineStr"/>
     </row>
     <row r="1040">
       <c r="A1040" t="n">
@@ -23420,6 +24465,7 @@
       <c r="F1040" t="n">
         <v>8</v>
       </c>
+      <c r="G1040" t="inlineStr"/>
     </row>
     <row r="1041">
       <c r="A1041" t="n">
@@ -23442,6 +24488,7 @@
       <c r="F1041" t="n">
         <v>8</v>
       </c>
+      <c r="G1041" t="inlineStr"/>
     </row>
     <row r="1042">
       <c r="A1042" t="n">
@@ -23464,6 +24511,7 @@
       <c r="F1042" t="n">
         <v>8</v>
       </c>
+      <c r="G1042" t="inlineStr"/>
     </row>
     <row r="1043">
       <c r="A1043" t="n">
@@ -23486,6 +24534,7 @@
       <c r="F1043" t="n">
         <v>8</v>
       </c>
+      <c r="G1043" t="inlineStr"/>
     </row>
     <row r="1044">
       <c r="A1044" t="n">
@@ -23508,6 +24557,7 @@
       <c r="F1044" t="n">
         <v>8</v>
       </c>
+      <c r="G1044" t="inlineStr"/>
     </row>
     <row r="1045">
       <c r="A1045" t="n">
@@ -23530,6 +24580,7 @@
       <c r="F1045" t="n">
         <v>8</v>
       </c>
+      <c r="G1045" t="inlineStr"/>
     </row>
     <row r="1046">
       <c r="A1046" t="n">
@@ -23552,6 +24603,7 @@
       <c r="F1046" t="n">
         <v>8</v>
       </c>
+      <c r="G1046" t="inlineStr"/>
     </row>
     <row r="1047">
       <c r="A1047" t="n">
@@ -23574,6 +24626,7 @@
       <c r="F1047" t="n">
         <v>8</v>
       </c>
+      <c r="G1047" t="inlineStr"/>
     </row>
     <row r="1048">
       <c r="A1048" t="n">
@@ -23596,6 +24649,7 @@
       <c r="F1048" t="n">
         <v>8</v>
       </c>
+      <c r="G1048" t="inlineStr"/>
     </row>
     <row r="1049">
       <c r="A1049" t="n">
@@ -23618,6 +24672,7 @@
       <c r="F1049" t="n">
         <v>8</v>
       </c>
+      <c r="G1049" t="inlineStr"/>
     </row>
     <row r="1050">
       <c r="A1050" t="n">
@@ -23640,6 +24695,7 @@
       <c r="F1050" t="n">
         <v>8</v>
       </c>
+      <c r="G1050" t="inlineStr"/>
     </row>
     <row r="1051">
       <c r="A1051" t="n">
@@ -23662,6 +24718,7 @@
       <c r="F1051" t="n">
         <v>8</v>
       </c>
+      <c r="G1051" t="inlineStr"/>
     </row>
     <row r="1052">
       <c r="A1052" t="n">
@@ -23684,6 +24741,7 @@
       <c r="F1052" t="n">
         <v>8</v>
       </c>
+      <c r="G1052" t="inlineStr"/>
     </row>
     <row r="1053">
       <c r="A1053" t="n">
@@ -23706,6 +24764,7 @@
       <c r="F1053" t="n">
         <v>8</v>
       </c>
+      <c r="G1053" t="inlineStr"/>
     </row>
     <row r="1054">
       <c r="A1054" t="n">
@@ -23728,6 +24787,7 @@
       <c r="F1054" t="n">
         <v>8</v>
       </c>
+      <c r="G1054" t="inlineStr"/>
     </row>
     <row r="1055">
       <c r="A1055" t="n">
@@ -23750,6 +24810,7 @@
       <c r="F1055" t="n">
         <v>8</v>
       </c>
+      <c r="G1055" t="inlineStr"/>
     </row>
     <row r="1056">
       <c r="A1056" t="n">
@@ -23772,6 +24833,7 @@
       <c r="F1056" t="n">
         <v>8</v>
       </c>
+      <c r="G1056" t="inlineStr"/>
     </row>
     <row r="1057">
       <c r="A1057" t="n">
@@ -23794,6 +24856,7 @@
       <c r="F1057" t="n">
         <v>8</v>
       </c>
+      <c r="G1057" t="inlineStr"/>
     </row>
     <row r="1058">
       <c r="A1058" t="n">
@@ -23816,6 +24879,7 @@
       <c r="F1058" t="n">
         <v>8</v>
       </c>
+      <c r="G1058" t="inlineStr"/>
     </row>
     <row r="1059">
       <c r="A1059" t="n">
@@ -23838,6 +24902,7 @@
       <c r="F1059" t="n">
         <v>8</v>
       </c>
+      <c r="G1059" t="inlineStr"/>
     </row>
     <row r="1060">
       <c r="A1060" t="n">
@@ -23860,6 +24925,7 @@
       <c r="F1060" t="n">
         <v>8</v>
       </c>
+      <c r="G1060" t="inlineStr"/>
     </row>
     <row r="1061">
       <c r="A1061" t="n">
@@ -23882,6 +24948,7 @@
       <c r="F1061" t="n">
         <v>8</v>
       </c>
+      <c r="G1061" t="inlineStr"/>
     </row>
     <row r="1062">
       <c r="A1062" t="n">
@@ -23904,6 +24971,7 @@
       <c r="F1062" t="n">
         <v>8</v>
       </c>
+      <c r="G1062" t="inlineStr"/>
     </row>
     <row r="1063">
       <c r="A1063" t="n">
@@ -23926,6 +24994,7 @@
       <c r="F1063" t="n">
         <v>8</v>
       </c>
+      <c r="G1063" t="inlineStr"/>
     </row>
     <row r="1064">
       <c r="A1064" t="n">
@@ -23948,6 +25017,7 @@
       <c r="F1064" t="n">
         <v>8</v>
       </c>
+      <c r="G1064" t="inlineStr"/>
     </row>
     <row r="1065">
       <c r="A1065" t="n">
@@ -23970,6 +25040,7 @@
       <c r="F1065" t="n">
         <v>8</v>
       </c>
+      <c r="G1065" t="inlineStr"/>
     </row>
     <row r="1066">
       <c r="A1066" t="n">
@@ -23992,6 +25063,7 @@
       <c r="F1066" t="n">
         <v>8</v>
       </c>
+      <c r="G1066" t="inlineStr"/>
     </row>
     <row r="1067">
       <c r="A1067" t="n">
@@ -24014,6 +25086,7 @@
       <c r="F1067" t="n">
         <v>8</v>
       </c>
+      <c r="G1067" t="inlineStr"/>
     </row>
     <row r="1068">
       <c r="A1068" t="n">
@@ -24036,6 +25109,7 @@
       <c r="F1068" t="n">
         <v>8</v>
       </c>
+      <c r="G1068" t="inlineStr"/>
     </row>
     <row r="1069">
       <c r="A1069" t="n">
@@ -24058,6 +25132,7 @@
       <c r="F1069" t="n">
         <v>8</v>
       </c>
+      <c r="G1069" t="inlineStr"/>
     </row>
     <row r="1070">
       <c r="A1070" t="n">
@@ -24080,6 +25155,7 @@
       <c r="F1070" t="n">
         <v>8</v>
       </c>
+      <c r="G1070" t="inlineStr"/>
     </row>
     <row r="1071">
       <c r="A1071" t="n">
@@ -24102,6 +25178,7 @@
       <c r="F1071" t="n">
         <v>8</v>
       </c>
+      <c r="G1071" t="inlineStr"/>
     </row>
     <row r="1072">
       <c r="A1072" t="n">
@@ -24124,6 +25201,7 @@
       <c r="F1072" t="n">
         <v>8</v>
       </c>
+      <c r="G1072" t="inlineStr"/>
     </row>
     <row r="1073">
       <c r="A1073" t="n">
@@ -24146,6 +25224,7 @@
       <c r="F1073" t="n">
         <v>8</v>
       </c>
+      <c r="G1073" t="inlineStr"/>
     </row>
     <row r="1074">
       <c r="A1074" t="n">
@@ -24168,6 +25247,7 @@
       <c r="F1074" t="n">
         <v>8</v>
       </c>
+      <c r="G1074" t="inlineStr"/>
     </row>
     <row r="1075">
       <c r="A1075" t="n">
@@ -24190,6 +25270,7 @@
       <c r="F1075" t="n">
         <v>8</v>
       </c>
+      <c r="G1075" t="inlineStr"/>
     </row>
     <row r="1076">
       <c r="A1076" t="n">
@@ -24212,6 +25293,7 @@
       <c r="F1076" t="n">
         <v>8</v>
       </c>
+      <c r="G1076" t="inlineStr"/>
     </row>
     <row r="1077">
       <c r="A1077" t="n">
@@ -24234,6 +25316,7 @@
       <c r="F1077" t="n">
         <v>8</v>
       </c>
+      <c r="G1077" t="inlineStr"/>
     </row>
     <row r="1078">
       <c r="A1078" t="n">
@@ -24256,6 +25339,7 @@
       <c r="F1078" t="n">
         <v>8</v>
       </c>
+      <c r="G1078" t="inlineStr"/>
     </row>
     <row r="1079">
       <c r="A1079" t="n">
@@ -24278,6 +25362,7 @@
       <c r="F1079" t="n">
         <v>8</v>
       </c>
+      <c r="G1079" t="inlineStr"/>
     </row>
     <row r="1080">
       <c r="A1080" t="n">
@@ -24300,6 +25385,7 @@
       <c r="F1080" t="n">
         <v>8</v>
       </c>
+      <c r="G1080" t="inlineStr"/>
     </row>
     <row r="1081">
       <c r="A1081" t="n">
@@ -24322,6 +25408,7 @@
       <c r="F1081" t="n">
         <v>8</v>
       </c>
+      <c r="G1081" t="inlineStr"/>
     </row>
     <row r="1082">
       <c r="A1082" t="n">
@@ -24344,6 +25431,7 @@
       <c r="F1082" t="n">
         <v>8</v>
       </c>
+      <c r="G1082" t="inlineStr"/>
     </row>
     <row r="1083">
       <c r="A1083" t="n">
@@ -24366,6 +25454,7 @@
       <c r="F1083" t="n">
         <v>8</v>
       </c>
+      <c r="G1083" t="inlineStr"/>
     </row>
     <row r="1084">
       <c r="A1084" t="n">
@@ -24388,6 +25477,7 @@
       <c r="F1084" t="n">
         <v>8</v>
       </c>
+      <c r="G1084" t="inlineStr"/>
     </row>
     <row r="1085">
       <c r="A1085" t="n">
@@ -24410,6 +25500,7 @@
       <c r="F1085" t="n">
         <v>8</v>
       </c>
+      <c r="G1085" t="inlineStr"/>
     </row>
     <row r="1086">
       <c r="A1086" t="n">
@@ -24432,6 +25523,7 @@
       <c r="F1086" t="n">
         <v>8</v>
       </c>
+      <c r="G1086" t="inlineStr"/>
     </row>
     <row r="1087">
       <c r="A1087" t="n">
@@ -24454,6 +25546,7 @@
       <c r="F1087" t="n">
         <v>8</v>
       </c>
+      <c r="G1087" t="inlineStr"/>
     </row>
     <row r="1088">
       <c r="A1088" t="n">
@@ -24476,6 +25569,7 @@
       <c r="F1088" t="n">
         <v>8</v>
       </c>
+      <c r="G1088" t="inlineStr"/>
     </row>
     <row r="1089">
       <c r="A1089" t="n">
@@ -24498,6 +25592,7 @@
       <c r="F1089" t="n">
         <v>8</v>
       </c>
+      <c r="G1089" t="inlineStr"/>
     </row>
     <row r="1090">
       <c r="A1090" t="n">
@@ -24520,6 +25615,7 @@
       <c r="F1090" t="n">
         <v>8</v>
       </c>
+      <c r="G1090" t="inlineStr"/>
     </row>
     <row r="1091">
       <c r="A1091" t="n">
@@ -24542,6 +25638,7 @@
       <c r="F1091" t="n">
         <v>8</v>
       </c>
+      <c r="G1091" t="inlineStr"/>
     </row>
     <row r="1092">
       <c r="A1092" t="n">
@@ -24564,6 +25661,7 @@
       <c r="F1092" t="n">
         <v>8</v>
       </c>
+      <c r="G1092" t="inlineStr"/>
     </row>
     <row r="1093">
       <c r="A1093" t="n">
@@ -24586,6 +25684,7 @@
       <c r="F1093" t="n">
         <v>8</v>
       </c>
+      <c r="G1093" t="inlineStr"/>
     </row>
     <row r="1094">
       <c r="A1094" t="n">
@@ -24608,6 +25707,7 @@
       <c r="F1094" t="n">
         <v>8</v>
       </c>
+      <c r="G1094" t="inlineStr"/>
     </row>
     <row r="1095">
       <c r="A1095" t="n">
@@ -24630,6 +25730,7 @@
       <c r="F1095" t="n">
         <v>8</v>
       </c>
+      <c r="G1095" t="inlineStr"/>
     </row>
     <row r="1096">
       <c r="A1096" t="n">
@@ -24652,6 +25753,7 @@
       <c r="F1096" t="n">
         <v>8</v>
       </c>
+      <c r="G1096" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
